--- a/pujk.xlsx
+++ b/pujk.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OJK\Penugasan 2\acara\gencar\monev\olah data\coding\running\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF2A6FAB-7FD0-46BC-8832-99C3E888CACA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC3A356A-2A00-49D8-9DE8-7D9604440174}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7238,9 +7238,6 @@
     <t>PT BPRS ATTAQWA</t>
   </si>
   <si>
-    <t>PT BPRS BERKAH RAMADHAN</t>
-  </si>
-  <si>
     <t>PT BPRS BINA AMWALUL HASANAH</t>
   </si>
   <si>
@@ -9021,6 +9018,9 @@
   </si>
   <si>
     <t>PT Fortuna Integritas Mandiri (ICEx)</t>
+  </si>
+  <si>
+    <t>PT BPRS FITRAH</t>
   </si>
 </sst>
 </file>
@@ -10647,7 +10647,7 @@
         <v>118</v>
       </c>
       <c r="B119" t="s">
-        <v>2906</v>
+        <v>2905</v>
       </c>
       <c r="C119" t="s">
         <v>97</v>
@@ -17522,7 +17522,7 @@
         <v>743</v>
       </c>
       <c r="B744" t="s">
-        <v>2907</v>
+        <v>2906</v>
       </c>
       <c r="C744" t="s">
         <v>293</v>
@@ -35573,7 +35573,7 @@
         <v>2384</v>
       </c>
       <c r="B2385" t="s">
-        <v>2401</v>
+        <v>2995</v>
       </c>
       <c r="C2385" t="s">
         <v>2389</v>
@@ -35584,7 +35584,7 @@
         <v>2385</v>
       </c>
       <c r="B2386" t="s">
-        <v>2402</v>
+        <v>2401</v>
       </c>
       <c r="C2386" t="s">
         <v>2389</v>
@@ -35595,7 +35595,7 @@
         <v>2386</v>
       </c>
       <c r="B2387" t="s">
-        <v>2403</v>
+        <v>2402</v>
       </c>
       <c r="C2387" t="s">
         <v>2389</v>
@@ -35606,7 +35606,7 @@
         <v>2387</v>
       </c>
       <c r="B2388" t="s">
-        <v>2404</v>
+        <v>2403</v>
       </c>
       <c r="C2388" t="s">
         <v>2389</v>
@@ -35617,7 +35617,7 @@
         <v>2388</v>
       </c>
       <c r="B2389" t="s">
-        <v>2405</v>
+        <v>2404</v>
       </c>
       <c r="C2389" t="s">
         <v>2389</v>
@@ -35628,7 +35628,7 @@
         <v>2389</v>
       </c>
       <c r="B2390" t="s">
-        <v>2406</v>
+        <v>2405</v>
       </c>
       <c r="C2390" t="s">
         <v>2389</v>
@@ -35639,7 +35639,7 @@
         <v>2390</v>
       </c>
       <c r="B2391" t="s">
-        <v>2407</v>
+        <v>2406</v>
       </c>
       <c r="C2391" t="s">
         <v>2389</v>
@@ -35650,7 +35650,7 @@
         <v>2391</v>
       </c>
       <c r="B2392" t="s">
-        <v>2408</v>
+        <v>2407</v>
       </c>
       <c r="C2392" t="s">
         <v>2389</v>
@@ -35661,7 +35661,7 @@
         <v>2392</v>
       </c>
       <c r="B2393" t="s">
-        <v>2409</v>
+        <v>2408</v>
       </c>
       <c r="C2393" t="s">
         <v>2389</v>
@@ -35672,7 +35672,7 @@
         <v>2393</v>
       </c>
       <c r="B2394" t="s">
-        <v>2410</v>
+        <v>2409</v>
       </c>
       <c r="C2394" t="s">
         <v>2389</v>
@@ -35683,7 +35683,7 @@
         <v>2394</v>
       </c>
       <c r="B2395" t="s">
-        <v>2411</v>
+        <v>2410</v>
       </c>
       <c r="C2395" t="s">
         <v>2389</v>
@@ -35694,7 +35694,7 @@
         <v>2395</v>
       </c>
       <c r="B2396" t="s">
-        <v>2412</v>
+        <v>2411</v>
       </c>
       <c r="C2396" t="s">
         <v>2389</v>
@@ -35705,7 +35705,7 @@
         <v>2396</v>
       </c>
       <c r="B2397" t="s">
-        <v>2413</v>
+        <v>2412</v>
       </c>
       <c r="C2397" t="s">
         <v>2389</v>
@@ -35716,7 +35716,7 @@
         <v>2397</v>
       </c>
       <c r="B2398" t="s">
-        <v>2414</v>
+        <v>2413</v>
       </c>
       <c r="C2398" t="s">
         <v>2389</v>
@@ -35727,7 +35727,7 @@
         <v>2398</v>
       </c>
       <c r="B2399" t="s">
-        <v>2415</v>
+        <v>2414</v>
       </c>
       <c r="C2399" t="s">
         <v>2389</v>
@@ -35738,7 +35738,7 @@
         <v>2399</v>
       </c>
       <c r="B2400" t="s">
-        <v>2416</v>
+        <v>2415</v>
       </c>
       <c r="C2400" t="s">
         <v>2389</v>
@@ -35749,7 +35749,7 @@
         <v>2400</v>
       </c>
       <c r="B2401" t="s">
-        <v>2417</v>
+        <v>2416</v>
       </c>
       <c r="C2401" t="s">
         <v>2389</v>
@@ -35760,7 +35760,7 @@
         <v>2401</v>
       </c>
       <c r="B2402" t="s">
-        <v>2418</v>
+        <v>2417</v>
       </c>
       <c r="C2402" t="s">
         <v>2389</v>
@@ -35771,7 +35771,7 @@
         <v>2402</v>
       </c>
       <c r="B2403" t="s">
-        <v>2419</v>
+        <v>2418</v>
       </c>
       <c r="C2403" t="s">
         <v>2389</v>
@@ -35782,7 +35782,7 @@
         <v>2403</v>
       </c>
       <c r="B2404" t="s">
-        <v>2420</v>
+        <v>2419</v>
       </c>
       <c r="C2404" t="s">
         <v>2389</v>
@@ -35793,7 +35793,7 @@
         <v>2404</v>
       </c>
       <c r="B2405" t="s">
-        <v>2421</v>
+        <v>2420</v>
       </c>
       <c r="C2405" t="s">
         <v>2389</v>
@@ -35804,7 +35804,7 @@
         <v>2405</v>
       </c>
       <c r="B2406" t="s">
-        <v>2422</v>
+        <v>2421</v>
       </c>
       <c r="C2406" t="s">
         <v>2389</v>
@@ -35815,7 +35815,7 @@
         <v>2406</v>
       </c>
       <c r="B2407" t="s">
-        <v>2423</v>
+        <v>2422</v>
       </c>
       <c r="C2407" t="s">
         <v>2389</v>
@@ -35826,7 +35826,7 @@
         <v>2407</v>
       </c>
       <c r="B2408" t="s">
-        <v>2424</v>
+        <v>2423</v>
       </c>
       <c r="C2408" t="s">
         <v>2389</v>
@@ -35837,7 +35837,7 @@
         <v>2408</v>
       </c>
       <c r="B2409" t="s">
-        <v>2425</v>
+        <v>2424</v>
       </c>
       <c r="C2409" t="s">
         <v>2389</v>
@@ -35848,7 +35848,7 @@
         <v>2409</v>
       </c>
       <c r="B2410" t="s">
-        <v>2426</v>
+        <v>2425</v>
       </c>
       <c r="C2410" t="s">
         <v>2389</v>
@@ -35859,7 +35859,7 @@
         <v>2410</v>
       </c>
       <c r="B2411" t="s">
-        <v>2427</v>
+        <v>2426</v>
       </c>
       <c r="C2411" t="s">
         <v>2389</v>
@@ -35870,7 +35870,7 @@
         <v>2411</v>
       </c>
       <c r="B2412" t="s">
-        <v>2428</v>
+        <v>2427</v>
       </c>
       <c r="C2412" t="s">
         <v>2389</v>
@@ -35881,7 +35881,7 @@
         <v>2412</v>
       </c>
       <c r="B2413" t="s">
-        <v>2429</v>
+        <v>2428</v>
       </c>
       <c r="C2413" t="s">
         <v>2389</v>
@@ -35892,7 +35892,7 @@
         <v>2413</v>
       </c>
       <c r="B2414" t="s">
-        <v>2430</v>
+        <v>2429</v>
       </c>
       <c r="C2414" t="s">
         <v>2389</v>
@@ -35903,7 +35903,7 @@
         <v>2414</v>
       </c>
       <c r="B2415" t="s">
-        <v>2431</v>
+        <v>2430</v>
       </c>
       <c r="C2415" t="s">
         <v>2389</v>
@@ -35914,7 +35914,7 @@
         <v>2415</v>
       </c>
       <c r="B2416" t="s">
-        <v>2432</v>
+        <v>2431</v>
       </c>
       <c r="C2416" t="s">
         <v>2389</v>
@@ -35925,7 +35925,7 @@
         <v>2416</v>
       </c>
       <c r="B2417" t="s">
-        <v>2433</v>
+        <v>2432</v>
       </c>
       <c r="C2417" t="s">
         <v>2389</v>
@@ -35936,7 +35936,7 @@
         <v>2417</v>
       </c>
       <c r="B2418" t="s">
-        <v>2434</v>
+        <v>2433</v>
       </c>
       <c r="C2418" t="s">
         <v>2389</v>
@@ -35947,7 +35947,7 @@
         <v>2418</v>
       </c>
       <c r="B2419" t="s">
-        <v>2435</v>
+        <v>2434</v>
       </c>
       <c r="C2419" t="s">
         <v>2389</v>
@@ -35958,7 +35958,7 @@
         <v>2419</v>
       </c>
       <c r="B2420" t="s">
-        <v>2436</v>
+        <v>2435</v>
       </c>
       <c r="C2420" t="s">
         <v>2389</v>
@@ -35969,7 +35969,7 @@
         <v>2420</v>
       </c>
       <c r="B2421" t="s">
-        <v>2437</v>
+        <v>2436</v>
       </c>
       <c r="C2421" t="s">
         <v>2389</v>
@@ -35980,7 +35980,7 @@
         <v>2421</v>
       </c>
       <c r="B2422" t="s">
-        <v>2438</v>
+        <v>2437</v>
       </c>
       <c r="C2422" t="s">
         <v>2389</v>
@@ -35991,7 +35991,7 @@
         <v>2422</v>
       </c>
       <c r="B2423" t="s">
-        <v>2439</v>
+        <v>2438</v>
       </c>
       <c r="C2423" t="s">
         <v>2389</v>
@@ -36002,7 +36002,7 @@
         <v>2423</v>
       </c>
       <c r="B2424" t="s">
-        <v>2440</v>
+        <v>2439</v>
       </c>
       <c r="C2424" t="s">
         <v>2389</v>
@@ -36013,7 +36013,7 @@
         <v>2424</v>
       </c>
       <c r="B2425" t="s">
-        <v>2441</v>
+        <v>2440</v>
       </c>
       <c r="C2425" t="s">
         <v>2389</v>
@@ -36024,7 +36024,7 @@
         <v>2425</v>
       </c>
       <c r="B2426" t="s">
-        <v>2442</v>
+        <v>2441</v>
       </c>
       <c r="C2426" t="s">
         <v>2389</v>
@@ -36035,7 +36035,7 @@
         <v>2426</v>
       </c>
       <c r="B2427" t="s">
-        <v>2443</v>
+        <v>2442</v>
       </c>
       <c r="C2427" t="s">
         <v>2389</v>
@@ -36046,7 +36046,7 @@
         <v>2427</v>
       </c>
       <c r="B2428" t="s">
-        <v>2444</v>
+        <v>2443</v>
       </c>
       <c r="C2428" t="s">
         <v>2389</v>
@@ -36057,7 +36057,7 @@
         <v>2428</v>
       </c>
       <c r="B2429" t="s">
-        <v>2445</v>
+        <v>2444</v>
       </c>
       <c r="C2429" t="s">
         <v>2389</v>
@@ -36068,7 +36068,7 @@
         <v>2429</v>
       </c>
       <c r="B2430" t="s">
-        <v>2446</v>
+        <v>2445</v>
       </c>
       <c r="C2430" t="s">
         <v>2389</v>
@@ -36079,7 +36079,7 @@
         <v>2430</v>
       </c>
       <c r="B2431" t="s">
-        <v>2447</v>
+        <v>2446</v>
       </c>
       <c r="C2431" t="s">
         <v>2389</v>
@@ -36090,7 +36090,7 @@
         <v>2431</v>
       </c>
       <c r="B2432" t="s">
-        <v>2448</v>
+        <v>2447</v>
       </c>
       <c r="C2432" t="s">
         <v>2389</v>
@@ -36101,7 +36101,7 @@
         <v>2432</v>
       </c>
       <c r="B2433" t="s">
-        <v>2449</v>
+        <v>2448</v>
       </c>
       <c r="C2433" t="s">
         <v>2389</v>
@@ -36112,7 +36112,7 @@
         <v>2433</v>
       </c>
       <c r="B2434" t="s">
-        <v>2450</v>
+        <v>2449</v>
       </c>
       <c r="C2434" t="s">
         <v>2389</v>
@@ -36123,7 +36123,7 @@
         <v>2434</v>
       </c>
       <c r="B2435" t="s">
-        <v>2451</v>
+        <v>2450</v>
       </c>
       <c r="C2435" t="s">
         <v>2389</v>
@@ -36134,7 +36134,7 @@
         <v>2435</v>
       </c>
       <c r="B2436" t="s">
-        <v>2452</v>
+        <v>2451</v>
       </c>
       <c r="C2436" t="s">
         <v>2389</v>
@@ -36145,7 +36145,7 @@
         <v>2436</v>
       </c>
       <c r="B2437" t="s">
-        <v>2453</v>
+        <v>2452</v>
       </c>
       <c r="C2437" t="s">
         <v>2389</v>
@@ -36156,7 +36156,7 @@
         <v>2437</v>
       </c>
       <c r="B2438" t="s">
-        <v>2439</v>
+        <v>2438</v>
       </c>
       <c r="C2438" t="s">
         <v>2389</v>
@@ -36167,7 +36167,7 @@
         <v>2438</v>
       </c>
       <c r="B2439" t="s">
-        <v>2440</v>
+        <v>2439</v>
       </c>
       <c r="C2439" t="s">
         <v>2389</v>
@@ -36178,7 +36178,7 @@
         <v>2439</v>
       </c>
       <c r="B2440" t="s">
-        <v>2441</v>
+        <v>2440</v>
       </c>
       <c r="C2440" t="s">
         <v>2389</v>
@@ -36189,7 +36189,7 @@
         <v>2440</v>
       </c>
       <c r="B2441" t="s">
-        <v>2442</v>
+        <v>2441</v>
       </c>
       <c r="C2441" t="s">
         <v>2389</v>
@@ -36200,7 +36200,7 @@
         <v>2441</v>
       </c>
       <c r="B2442" t="s">
-        <v>2443</v>
+        <v>2442</v>
       </c>
       <c r="C2442" t="s">
         <v>2389</v>
@@ -36211,7 +36211,7 @@
         <v>2442</v>
       </c>
       <c r="B2443" t="s">
-        <v>2444</v>
+        <v>2443</v>
       </c>
       <c r="C2443" t="s">
         <v>2389</v>
@@ -36222,7 +36222,7 @@
         <v>2443</v>
       </c>
       <c r="B2444" t="s">
-        <v>2445</v>
+        <v>2444</v>
       </c>
       <c r="C2444" t="s">
         <v>2389</v>
@@ -36233,7 +36233,7 @@
         <v>2444</v>
       </c>
       <c r="B2445" t="s">
-        <v>2454</v>
+        <v>2453</v>
       </c>
       <c r="C2445" t="s">
         <v>2389</v>
@@ -36244,7 +36244,7 @@
         <v>2445</v>
       </c>
       <c r="B2446" t="s">
-        <v>2455</v>
+        <v>2454</v>
       </c>
       <c r="C2446" t="s">
         <v>2389</v>
@@ -36255,7 +36255,7 @@
         <v>2446</v>
       </c>
       <c r="B2447" t="s">
-        <v>2456</v>
+        <v>2455</v>
       </c>
       <c r="C2447" t="s">
         <v>2389</v>
@@ -36266,7 +36266,7 @@
         <v>2447</v>
       </c>
       <c r="B2448" t="s">
-        <v>2457</v>
+        <v>2456</v>
       </c>
       <c r="C2448" t="s">
         <v>2389</v>
@@ -36277,7 +36277,7 @@
         <v>2448</v>
       </c>
       <c r="B2449" t="s">
-        <v>2458</v>
+        <v>2457</v>
       </c>
       <c r="C2449" t="s">
         <v>2389</v>
@@ -36288,7 +36288,7 @@
         <v>2449</v>
       </c>
       <c r="B2450" t="s">
-        <v>2459</v>
+        <v>2458</v>
       </c>
       <c r="C2450" t="s">
         <v>2389</v>
@@ -36299,7 +36299,7 @@
         <v>2450</v>
       </c>
       <c r="B2451" t="s">
-        <v>2460</v>
+        <v>2459</v>
       </c>
       <c r="C2451" t="s">
         <v>2389</v>
@@ -36310,7 +36310,7 @@
         <v>2451</v>
       </c>
       <c r="B2452" t="s">
-        <v>2461</v>
+        <v>2460</v>
       </c>
       <c r="C2452" t="s">
         <v>2389</v>
@@ -36321,7 +36321,7 @@
         <v>2452</v>
       </c>
       <c r="B2453" t="s">
-        <v>2462</v>
+        <v>2461</v>
       </c>
       <c r="C2453" t="s">
         <v>2389</v>
@@ -36332,7 +36332,7 @@
         <v>2453</v>
       </c>
       <c r="B2454" t="s">
-        <v>2463</v>
+        <v>2462</v>
       </c>
       <c r="C2454" t="s">
         <v>2389</v>
@@ -36343,7 +36343,7 @@
         <v>2454</v>
       </c>
       <c r="B2455" t="s">
-        <v>2464</v>
+        <v>2463</v>
       </c>
       <c r="C2455" t="s">
         <v>2389</v>
@@ -36354,7 +36354,7 @@
         <v>2455</v>
       </c>
       <c r="B2456" t="s">
-        <v>2465</v>
+        <v>2464</v>
       </c>
       <c r="C2456" t="s">
         <v>2389</v>
@@ -36365,7 +36365,7 @@
         <v>2456</v>
       </c>
       <c r="B2457" t="s">
-        <v>2466</v>
+        <v>2465</v>
       </c>
       <c r="C2457" t="s">
         <v>2389</v>
@@ -36376,7 +36376,7 @@
         <v>2457</v>
       </c>
       <c r="B2458" t="s">
-        <v>2467</v>
+        <v>2466</v>
       </c>
       <c r="C2458" t="s">
         <v>2389</v>
@@ -36387,7 +36387,7 @@
         <v>2458</v>
       </c>
       <c r="B2459" t="s">
-        <v>2468</v>
+        <v>2467</v>
       </c>
       <c r="C2459" t="s">
         <v>2389</v>
@@ -36398,7 +36398,7 @@
         <v>2459</v>
       </c>
       <c r="B2460" t="s">
-        <v>2469</v>
+        <v>2468</v>
       </c>
       <c r="C2460" t="s">
         <v>2389</v>
@@ -36409,7 +36409,7 @@
         <v>2460</v>
       </c>
       <c r="B2461" t="s">
-        <v>2470</v>
+        <v>2469</v>
       </c>
       <c r="C2461" t="s">
         <v>2389</v>
@@ -36420,7 +36420,7 @@
         <v>2461</v>
       </c>
       <c r="B2462" t="s">
-        <v>2471</v>
+        <v>2470</v>
       </c>
       <c r="C2462" t="s">
         <v>2389</v>
@@ -36431,7 +36431,7 @@
         <v>2462</v>
       </c>
       <c r="B2463" t="s">
-        <v>2472</v>
+        <v>2471</v>
       </c>
       <c r="C2463" t="s">
         <v>2389</v>
@@ -36442,7 +36442,7 @@
         <v>2463</v>
       </c>
       <c r="B2464" t="s">
-        <v>2473</v>
+        <v>2472</v>
       </c>
       <c r="C2464" t="s">
         <v>2389</v>
@@ -36453,7 +36453,7 @@
         <v>2464</v>
       </c>
       <c r="B2465" t="s">
-        <v>2474</v>
+        <v>2473</v>
       </c>
       <c r="C2465" t="s">
         <v>2389</v>
@@ -36464,7 +36464,7 @@
         <v>2465</v>
       </c>
       <c r="B2466" t="s">
-        <v>2475</v>
+        <v>2474</v>
       </c>
       <c r="C2466" t="s">
         <v>2389</v>
@@ -36475,7 +36475,7 @@
         <v>2466</v>
       </c>
       <c r="B2467" t="s">
-        <v>2476</v>
+        <v>2475</v>
       </c>
       <c r="C2467" t="s">
         <v>2389</v>
@@ -36486,7 +36486,7 @@
         <v>2467</v>
       </c>
       <c r="B2468" t="s">
-        <v>2477</v>
+        <v>2476</v>
       </c>
       <c r="C2468" t="s">
         <v>2389</v>
@@ -36497,7 +36497,7 @@
         <v>2468</v>
       </c>
       <c r="B2469" t="s">
-        <v>2478</v>
+        <v>2477</v>
       </c>
       <c r="C2469" t="s">
         <v>2389</v>
@@ -36508,7 +36508,7 @@
         <v>2469</v>
       </c>
       <c r="B2470" t="s">
-        <v>2479</v>
+        <v>2478</v>
       </c>
       <c r="C2470" t="s">
         <v>2389</v>
@@ -36519,7 +36519,7 @@
         <v>2470</v>
       </c>
       <c r="B2471" t="s">
-        <v>2480</v>
+        <v>2479</v>
       </c>
       <c r="C2471" t="s">
         <v>2389</v>
@@ -36530,7 +36530,7 @@
         <v>2471</v>
       </c>
       <c r="B2472" t="s">
-        <v>2481</v>
+        <v>2480</v>
       </c>
       <c r="C2472" t="s">
         <v>2389</v>
@@ -36541,7 +36541,7 @@
         <v>2472</v>
       </c>
       <c r="B2473" t="s">
-        <v>2482</v>
+        <v>2481</v>
       </c>
       <c r="C2473" t="s">
         <v>2389</v>
@@ -36552,7 +36552,7 @@
         <v>2473</v>
       </c>
       <c r="B2474" t="s">
-        <v>2483</v>
+        <v>2482</v>
       </c>
       <c r="C2474" t="s">
         <v>2389</v>
@@ -36563,7 +36563,7 @@
         <v>2474</v>
       </c>
       <c r="B2475" t="s">
-        <v>2484</v>
+        <v>2483</v>
       </c>
       <c r="C2475" t="s">
         <v>2389</v>
@@ -36574,7 +36574,7 @@
         <v>2475</v>
       </c>
       <c r="B2476" t="s">
-        <v>2485</v>
+        <v>2484</v>
       </c>
       <c r="C2476" t="s">
         <v>2389</v>
@@ -36585,7 +36585,7 @@
         <v>2476</v>
       </c>
       <c r="B2477" t="s">
-        <v>2486</v>
+        <v>2485</v>
       </c>
       <c r="C2477" t="s">
         <v>2389</v>
@@ -36596,7 +36596,7 @@
         <v>2477</v>
       </c>
       <c r="B2478" t="s">
-        <v>2487</v>
+        <v>2486</v>
       </c>
       <c r="C2478" t="s">
         <v>2389</v>
@@ -36607,7 +36607,7 @@
         <v>2478</v>
       </c>
       <c r="B2479" t="s">
-        <v>2488</v>
+        <v>2487</v>
       </c>
       <c r="C2479" t="s">
         <v>2389</v>
@@ -36618,7 +36618,7 @@
         <v>2479</v>
       </c>
       <c r="B2480" t="s">
-        <v>2489</v>
+        <v>2488</v>
       </c>
       <c r="C2480" t="s">
         <v>2389</v>
@@ -36629,7 +36629,7 @@
         <v>2480</v>
       </c>
       <c r="B2481" t="s">
-        <v>2490</v>
+        <v>2489</v>
       </c>
       <c r="C2481" t="s">
         <v>2389</v>
@@ -36640,7 +36640,7 @@
         <v>2481</v>
       </c>
       <c r="B2482" t="s">
-        <v>2491</v>
+        <v>2490</v>
       </c>
       <c r="C2482" t="s">
         <v>2389</v>
@@ -36651,7 +36651,7 @@
         <v>2482</v>
       </c>
       <c r="B2483" t="s">
-        <v>2492</v>
+        <v>2491</v>
       </c>
       <c r="C2483" t="s">
         <v>2389</v>
@@ -36662,7 +36662,7 @@
         <v>2483</v>
       </c>
       <c r="B2484" t="s">
-        <v>2493</v>
+        <v>2492</v>
       </c>
       <c r="C2484" t="s">
         <v>2389</v>
@@ -36673,7 +36673,7 @@
         <v>2484</v>
       </c>
       <c r="B2485" t="s">
-        <v>2494</v>
+        <v>2493</v>
       </c>
       <c r="C2485" t="s">
         <v>2389</v>
@@ -36684,7 +36684,7 @@
         <v>2485</v>
       </c>
       <c r="B2486" t="s">
-        <v>2495</v>
+        <v>2494</v>
       </c>
       <c r="C2486" t="s">
         <v>2389</v>
@@ -36695,7 +36695,7 @@
         <v>2486</v>
       </c>
       <c r="B2487" t="s">
-        <v>2496</v>
+        <v>2495</v>
       </c>
       <c r="C2487" t="s">
         <v>2389</v>
@@ -36706,7 +36706,7 @@
         <v>2487</v>
       </c>
       <c r="B2488" t="s">
-        <v>2497</v>
+        <v>2496</v>
       </c>
       <c r="C2488" t="s">
         <v>2389</v>
@@ -36717,7 +36717,7 @@
         <v>2488</v>
       </c>
       <c r="B2489" t="s">
-        <v>2498</v>
+        <v>2497</v>
       </c>
       <c r="C2489" t="s">
         <v>2389</v>
@@ -36728,7 +36728,7 @@
         <v>2489</v>
       </c>
       <c r="B2490" t="s">
-        <v>2499</v>
+        <v>2498</v>
       </c>
       <c r="C2490" t="s">
         <v>2389</v>
@@ -36739,7 +36739,7 @@
         <v>2490</v>
       </c>
       <c r="B2491" t="s">
-        <v>2500</v>
+        <v>2499</v>
       </c>
       <c r="C2491" t="s">
         <v>2389</v>
@@ -36750,7 +36750,7 @@
         <v>2491</v>
       </c>
       <c r="B2492" t="s">
-        <v>2501</v>
+        <v>2500</v>
       </c>
       <c r="C2492" t="s">
         <v>2389</v>
@@ -36761,7 +36761,7 @@
         <v>2492</v>
       </c>
       <c r="B2493" t="s">
-        <v>2502</v>
+        <v>2501</v>
       </c>
       <c r="C2493" t="s">
         <v>2389</v>
@@ -36772,7 +36772,7 @@
         <v>2493</v>
       </c>
       <c r="B2494" t="s">
-        <v>2503</v>
+        <v>2502</v>
       </c>
       <c r="C2494" t="s">
         <v>2389</v>
@@ -36783,7 +36783,7 @@
         <v>2494</v>
       </c>
       <c r="B2495" t="s">
-        <v>2504</v>
+        <v>2503</v>
       </c>
       <c r="C2495" t="s">
         <v>2389</v>
@@ -36794,7 +36794,7 @@
         <v>2495</v>
       </c>
       <c r="B2496" t="s">
-        <v>2505</v>
+        <v>2504</v>
       </c>
       <c r="C2496" t="s">
         <v>2389</v>
@@ -36805,7 +36805,7 @@
         <v>2496</v>
       </c>
       <c r="B2497" t="s">
-        <v>2506</v>
+        <v>2505</v>
       </c>
       <c r="C2497" t="s">
         <v>2389</v>
@@ -36816,7 +36816,7 @@
         <v>2497</v>
       </c>
       <c r="B2498" t="s">
-        <v>2507</v>
+        <v>2506</v>
       </c>
       <c r="C2498" t="s">
         <v>2389</v>
@@ -36827,7 +36827,7 @@
         <v>2498</v>
       </c>
       <c r="B2499" t="s">
-        <v>2508</v>
+        <v>2507</v>
       </c>
       <c r="C2499" t="s">
         <v>2389</v>
@@ -36838,7 +36838,7 @@
         <v>2499</v>
       </c>
       <c r="B2500" t="s">
-        <v>2509</v>
+        <v>2508</v>
       </c>
       <c r="C2500" t="s">
         <v>2389</v>
@@ -36849,7 +36849,7 @@
         <v>2500</v>
       </c>
       <c r="B2501" t="s">
-        <v>2510</v>
+        <v>2509</v>
       </c>
       <c r="C2501" t="s">
         <v>2389</v>
@@ -36860,7 +36860,7 @@
         <v>2501</v>
       </c>
       <c r="B2502" t="s">
-        <v>2511</v>
+        <v>2510</v>
       </c>
       <c r="C2502" t="s">
         <v>2389</v>
@@ -36871,7 +36871,7 @@
         <v>2502</v>
       </c>
       <c r="B2503" t="s">
-        <v>2512</v>
+        <v>2511</v>
       </c>
       <c r="C2503" t="s">
         <v>2389</v>
@@ -36882,7 +36882,7 @@
         <v>2503</v>
       </c>
       <c r="B2504" t="s">
-        <v>2513</v>
+        <v>2512</v>
       </c>
       <c r="C2504" t="s">
         <v>2389</v>
@@ -36893,7 +36893,7 @@
         <v>2504</v>
       </c>
       <c r="B2505" t="s">
-        <v>2514</v>
+        <v>2513</v>
       </c>
       <c r="C2505" t="s">
         <v>2389</v>
@@ -36904,7 +36904,7 @@
         <v>2505</v>
       </c>
       <c r="B2506" t="s">
-        <v>2515</v>
+        <v>2514</v>
       </c>
       <c r="C2506" t="s">
         <v>2389</v>
@@ -36915,7 +36915,7 @@
         <v>2506</v>
       </c>
       <c r="B2507" t="s">
-        <v>2516</v>
+        <v>2515</v>
       </c>
       <c r="C2507" t="s">
         <v>2389</v>
@@ -36926,7 +36926,7 @@
         <v>2507</v>
       </c>
       <c r="B2508" t="s">
-        <v>2517</v>
+        <v>2516</v>
       </c>
       <c r="C2508" t="s">
         <v>2389</v>
@@ -36937,7 +36937,7 @@
         <v>2508</v>
       </c>
       <c r="B2509" t="s">
-        <v>2518</v>
+        <v>2517</v>
       </c>
       <c r="C2509" t="s">
         <v>2389</v>
@@ -36948,7 +36948,7 @@
         <v>2509</v>
       </c>
       <c r="B2510" t="s">
-        <v>2519</v>
+        <v>2518</v>
       </c>
       <c r="C2510" t="s">
         <v>2389</v>
@@ -36959,7 +36959,7 @@
         <v>2510</v>
       </c>
       <c r="B2511" t="s">
-        <v>2520</v>
+        <v>2519</v>
       </c>
       <c r="C2511" t="s">
         <v>2389</v>
@@ -36970,7 +36970,7 @@
         <v>2511</v>
       </c>
       <c r="B2512" t="s">
-        <v>2521</v>
+        <v>2520</v>
       </c>
       <c r="C2512" t="s">
         <v>2389</v>
@@ -36981,7 +36981,7 @@
         <v>2512</v>
       </c>
       <c r="B2513" t="s">
-        <v>2522</v>
+        <v>2521</v>
       </c>
       <c r="C2513" t="s">
         <v>2389</v>
@@ -36992,7 +36992,7 @@
         <v>2513</v>
       </c>
       <c r="B2514" t="s">
-        <v>2523</v>
+        <v>2522</v>
       </c>
       <c r="C2514" t="s">
         <v>2389</v>
@@ -37003,7 +37003,7 @@
         <v>2514</v>
       </c>
       <c r="B2515" t="s">
-        <v>2524</v>
+        <v>2523</v>
       </c>
       <c r="C2515" t="s">
         <v>2389</v>
@@ -37014,7 +37014,7 @@
         <v>2515</v>
       </c>
       <c r="B2516" t="s">
-        <v>2525</v>
+        <v>2524</v>
       </c>
       <c r="C2516" t="s">
         <v>2389</v>
@@ -37025,7 +37025,7 @@
         <v>2516</v>
       </c>
       <c r="B2517" t="s">
-        <v>2526</v>
+        <v>2525</v>
       </c>
       <c r="C2517" t="s">
         <v>2389</v>
@@ -37036,7 +37036,7 @@
         <v>2517</v>
       </c>
       <c r="B2518" t="s">
-        <v>2527</v>
+        <v>2526</v>
       </c>
       <c r="C2518" t="s">
         <v>2389</v>
@@ -37047,7 +37047,7 @@
         <v>2518</v>
       </c>
       <c r="B2519" t="s">
-        <v>2528</v>
+        <v>2527</v>
       </c>
       <c r="C2519" t="s">
         <v>2389</v>
@@ -37058,7 +37058,7 @@
         <v>2519</v>
       </c>
       <c r="B2520" t="s">
-        <v>2529</v>
+        <v>2528</v>
       </c>
       <c r="C2520" t="s">
         <v>2389</v>
@@ -37069,7 +37069,7 @@
         <v>2520</v>
       </c>
       <c r="B2521" t="s">
-        <v>2530</v>
+        <v>2529</v>
       </c>
       <c r="C2521" t="s">
         <v>2389</v>
@@ -37080,7 +37080,7 @@
         <v>2521</v>
       </c>
       <c r="B2522" t="s">
-        <v>2531</v>
+        <v>2530</v>
       </c>
       <c r="C2522" t="s">
         <v>2389</v>
@@ -37091,7 +37091,7 @@
         <v>2522</v>
       </c>
       <c r="B2523" t="s">
-        <v>2532</v>
+        <v>2531</v>
       </c>
       <c r="C2523" t="s">
         <v>2389</v>
@@ -37102,7 +37102,7 @@
         <v>2523</v>
       </c>
       <c r="B2524" t="s">
-        <v>2533</v>
+        <v>2532</v>
       </c>
       <c r="C2524" t="s">
         <v>2389</v>
@@ -37113,7 +37113,7 @@
         <v>2524</v>
       </c>
       <c r="B2525" t="s">
-        <v>2534</v>
+        <v>2533</v>
       </c>
       <c r="C2525" t="s">
         <v>2389</v>
@@ -37124,7 +37124,7 @@
         <v>2525</v>
       </c>
       <c r="B2526" t="s">
-        <v>2535</v>
+        <v>2534</v>
       </c>
       <c r="C2526" t="s">
         <v>2389</v>
@@ -37135,7 +37135,7 @@
         <v>2526</v>
       </c>
       <c r="B2527" t="s">
-        <v>2536</v>
+        <v>2535</v>
       </c>
       <c r="C2527" t="s">
         <v>2389</v>
@@ -37146,7 +37146,7 @@
         <v>2527</v>
       </c>
       <c r="B2528" t="s">
-        <v>2537</v>
+        <v>2536</v>
       </c>
       <c r="C2528" t="s">
         <v>2389</v>
@@ -37157,7 +37157,7 @@
         <v>2528</v>
       </c>
       <c r="B2529" t="s">
-        <v>2538</v>
+        <v>2537</v>
       </c>
       <c r="C2529" t="s">
         <v>2389</v>
@@ -37168,7 +37168,7 @@
         <v>2529</v>
       </c>
       <c r="B2530" t="s">
-        <v>2539</v>
+        <v>2538</v>
       </c>
       <c r="C2530" t="s">
         <v>2389</v>
@@ -37179,7 +37179,7 @@
         <v>2530</v>
       </c>
       <c r="B2531" t="s">
-        <v>2540</v>
+        <v>2539</v>
       </c>
       <c r="C2531" t="s">
         <v>2389</v>
@@ -37190,7 +37190,7 @@
         <v>2531</v>
       </c>
       <c r="B2532" t="s">
-        <v>2541</v>
+        <v>2540</v>
       </c>
       <c r="C2532" t="s">
         <v>2389</v>
@@ -37201,7 +37201,7 @@
         <v>2532</v>
       </c>
       <c r="B2533" t="s">
-        <v>2542</v>
+        <v>2541</v>
       </c>
       <c r="C2533" t="s">
         <v>2389</v>
@@ -37212,7 +37212,7 @@
         <v>2533</v>
       </c>
       <c r="B2534" t="s">
-        <v>2543</v>
+        <v>2542</v>
       </c>
       <c r="C2534" t="s">
         <v>2389</v>
@@ -37223,7 +37223,7 @@
         <v>2534</v>
       </c>
       <c r="B2535" t="s">
-        <v>2544</v>
+        <v>2543</v>
       </c>
       <c r="C2535" t="s">
         <v>2389</v>
@@ -37234,7 +37234,7 @@
         <v>2535</v>
       </c>
       <c r="B2536" t="s">
-        <v>2545</v>
+        <v>2544</v>
       </c>
       <c r="C2536" t="s">
         <v>2389</v>
@@ -37245,7 +37245,7 @@
         <v>2536</v>
       </c>
       <c r="B2537" t="s">
-        <v>2546</v>
+        <v>2545</v>
       </c>
       <c r="C2537" t="s">
         <v>2389</v>
@@ -37256,7 +37256,7 @@
         <v>2537</v>
       </c>
       <c r="B2538" t="s">
-        <v>2547</v>
+        <v>2546</v>
       </c>
       <c r="C2538" t="s">
         <v>2389</v>
@@ -37267,7 +37267,7 @@
         <v>2538</v>
       </c>
       <c r="B2539" t="s">
-        <v>2548</v>
+        <v>2547</v>
       </c>
       <c r="C2539" t="s">
         <v>2389</v>
@@ -37278,7 +37278,7 @@
         <v>2539</v>
       </c>
       <c r="B2540" t="s">
-        <v>2549</v>
+        <v>2548</v>
       </c>
       <c r="C2540" t="s">
         <v>2389</v>
@@ -37289,7 +37289,7 @@
         <v>2540</v>
       </c>
       <c r="B2541" t="s">
-        <v>2550</v>
+        <v>2549</v>
       </c>
       <c r="C2541" t="s">
         <v>2389</v>
@@ -37300,7 +37300,7 @@
         <v>2541</v>
       </c>
       <c r="B2542" t="s">
-        <v>2551</v>
+        <v>2550</v>
       </c>
       <c r="C2542" t="s">
         <v>2389</v>
@@ -37311,7 +37311,7 @@
         <v>2542</v>
       </c>
       <c r="B2543" t="s">
-        <v>2552</v>
+        <v>2551</v>
       </c>
       <c r="C2543" t="s">
         <v>2389</v>
@@ -37322,7 +37322,7 @@
         <v>2543</v>
       </c>
       <c r="B2544" t="s">
-        <v>2553</v>
+        <v>2552</v>
       </c>
       <c r="C2544" t="s">
         <v>2389</v>
@@ -37333,7 +37333,7 @@
         <v>2544</v>
       </c>
       <c r="B2545" t="s">
-        <v>2554</v>
+        <v>2553</v>
       </c>
       <c r="C2545" t="s">
         <v>2389</v>
@@ -37344,7 +37344,7 @@
         <v>2545</v>
       </c>
       <c r="B2546" t="s">
-        <v>2555</v>
+        <v>2554</v>
       </c>
       <c r="C2546" t="s">
         <v>2389</v>
@@ -37355,7 +37355,7 @@
         <v>2546</v>
       </c>
       <c r="B2547" t="s">
-        <v>2556</v>
+        <v>2555</v>
       </c>
       <c r="C2547" t="s">
         <v>2389</v>
@@ -37366,7 +37366,7 @@
         <v>2547</v>
       </c>
       <c r="B2548" t="s">
-        <v>2557</v>
+        <v>2556</v>
       </c>
       <c r="C2548" t="s">
         <v>2389</v>
@@ -37377,7 +37377,7 @@
         <v>2548</v>
       </c>
       <c r="B2549" t="s">
-        <v>2558</v>
+        <v>2557</v>
       </c>
       <c r="C2549" t="s">
         <v>2389</v>
@@ -37388,7 +37388,7 @@
         <v>2549</v>
       </c>
       <c r="B2550" t="s">
-        <v>2559</v>
+        <v>2558</v>
       </c>
       <c r="C2550" t="s">
         <v>2389</v>
@@ -37399,7 +37399,7 @@
         <v>2550</v>
       </c>
       <c r="B2551" t="s">
-        <v>2560</v>
+        <v>2559</v>
       </c>
       <c r="C2551" t="s">
         <v>2389</v>
@@ -37410,7 +37410,7 @@
         <v>2551</v>
       </c>
       <c r="B2552" t="s">
-        <v>2561</v>
+        <v>2560</v>
       </c>
       <c r="C2552" t="s">
         <v>2389</v>
@@ -37421,10 +37421,10 @@
         <v>2552</v>
       </c>
       <c r="B2553" t="s">
+        <v>2561</v>
+      </c>
+      <c r="C2553" t="s">
         <v>2562</v>
-      </c>
-      <c r="C2553" t="s">
-        <v>2563</v>
       </c>
     </row>
     <row r="2554" spans="1:3" x14ac:dyDescent="0.3">
@@ -37432,10 +37432,10 @@
         <v>2553</v>
       </c>
       <c r="B2554" t="s">
+        <v>2563</v>
+      </c>
+      <c r="C2554" t="s">
         <v>2564</v>
-      </c>
-      <c r="C2554" t="s">
-        <v>2565</v>
       </c>
     </row>
     <row r="2555" spans="1:3" x14ac:dyDescent="0.3">
@@ -37443,10 +37443,10 @@
         <v>2554</v>
       </c>
       <c r="B2555" t="s">
-        <v>2566</v>
+        <v>2565</v>
       </c>
       <c r="C2555" t="s">
-        <v>2565</v>
+        <v>2564</v>
       </c>
     </row>
     <row r="2556" spans="1:3" x14ac:dyDescent="0.3">
@@ -37454,10 +37454,10 @@
         <v>2555</v>
       </c>
       <c r="B2556" t="s">
-        <v>2567</v>
+        <v>2566</v>
       </c>
       <c r="C2556" t="s">
-        <v>2565</v>
+        <v>2564</v>
       </c>
     </row>
     <row r="2557" spans="1:3" x14ac:dyDescent="0.3">
@@ -37465,10 +37465,10 @@
         <v>2556</v>
       </c>
       <c r="B2557" t="s">
+        <v>2567</v>
+      </c>
+      <c r="C2557" t="s">
         <v>2568</v>
-      </c>
-      <c r="C2557" t="s">
-        <v>2569</v>
       </c>
     </row>
     <row r="2558" spans="1:3" x14ac:dyDescent="0.3">
@@ -37476,10 +37476,10 @@
         <v>2557</v>
       </c>
       <c r="B2558" t="s">
-        <v>2570</v>
+        <v>2569</v>
       </c>
       <c r="C2558" t="s">
-        <v>2569</v>
+        <v>2568</v>
       </c>
     </row>
     <row r="2559" spans="1:3" x14ac:dyDescent="0.3">
@@ -37487,10 +37487,10 @@
         <v>2558</v>
       </c>
       <c r="B2559" t="s">
-        <v>2571</v>
+        <v>2570</v>
       </c>
       <c r="C2559" t="s">
-        <v>2569</v>
+        <v>2568</v>
       </c>
     </row>
     <row r="2560" spans="1:3" x14ac:dyDescent="0.3">
@@ -37498,10 +37498,10 @@
         <v>2559</v>
       </c>
       <c r="B2560" t="s">
-        <v>2572</v>
+        <v>2571</v>
       </c>
       <c r="C2560" t="s">
-        <v>2569</v>
+        <v>2568</v>
       </c>
     </row>
     <row r="2561" spans="1:3" x14ac:dyDescent="0.3">
@@ -37509,10 +37509,10 @@
         <v>2560</v>
       </c>
       <c r="B2561" t="s">
-        <v>2573</v>
+        <v>2572</v>
       </c>
       <c r="C2561" t="s">
-        <v>2569</v>
+        <v>2568</v>
       </c>
     </row>
     <row r="2562" spans="1:3" x14ac:dyDescent="0.3">
@@ -37520,10 +37520,10 @@
         <v>2561</v>
       </c>
       <c r="B2562" t="s">
-        <v>2574</v>
+        <v>2573</v>
       </c>
       <c r="C2562" t="s">
-        <v>2569</v>
+        <v>2568</v>
       </c>
     </row>
     <row r="2563" spans="1:3" x14ac:dyDescent="0.3">
@@ -37531,10 +37531,10 @@
         <v>2562</v>
       </c>
       <c r="B2563" t="s">
-        <v>2575</v>
+        <v>2574</v>
       </c>
       <c r="C2563" t="s">
-        <v>2569</v>
+        <v>2568</v>
       </c>
     </row>
     <row r="2564" spans="1:3" x14ac:dyDescent="0.3">
@@ -37542,10 +37542,10 @@
         <v>2563</v>
       </c>
       <c r="B2564" t="s">
+        <v>2575</v>
+      </c>
+      <c r="C2564" t="s">
         <v>2576</v>
-      </c>
-      <c r="C2564" t="s">
-        <v>2577</v>
       </c>
     </row>
     <row r="2565" spans="1:3" x14ac:dyDescent="0.3">
@@ -37553,10 +37553,10 @@
         <v>2564</v>
       </c>
       <c r="B2565" t="s">
+        <v>2577</v>
+      </c>
+      <c r="C2565" t="s">
         <v>2578</v>
-      </c>
-      <c r="C2565" t="s">
-        <v>2579</v>
       </c>
     </row>
     <row r="2566" spans="1:3" x14ac:dyDescent="0.3">
@@ -37564,10 +37564,10 @@
         <v>2565</v>
       </c>
       <c r="B2566" t="s">
-        <v>2580</v>
+        <v>2579</v>
       </c>
       <c r="C2566" t="s">
-        <v>2579</v>
+        <v>2578</v>
       </c>
     </row>
     <row r="2567" spans="1:3" x14ac:dyDescent="0.3">
@@ -37575,10 +37575,10 @@
         <v>2566</v>
       </c>
       <c r="B2567" t="s">
+        <v>2580</v>
+      </c>
+      <c r="C2567" t="s">
         <v>2581</v>
-      </c>
-      <c r="C2567" t="s">
-        <v>2582</v>
       </c>
     </row>
     <row r="2568" spans="1:3" x14ac:dyDescent="0.3">
@@ -37586,10 +37586,10 @@
         <v>2567</v>
       </c>
       <c r="B2568" t="s">
-        <v>2583</v>
+        <v>2582</v>
       </c>
       <c r="C2568" t="s">
-        <v>2582</v>
+        <v>2581</v>
       </c>
     </row>
     <row r="2569" spans="1:3" x14ac:dyDescent="0.3">
@@ -37597,10 +37597,10 @@
         <v>2568</v>
       </c>
       <c r="B2569" t="s">
-        <v>2584</v>
+        <v>2583</v>
       </c>
       <c r="C2569" t="s">
-        <v>2582</v>
+        <v>2581</v>
       </c>
     </row>
     <row r="2570" spans="1:3" x14ac:dyDescent="0.3">
@@ -37608,10 +37608,10 @@
         <v>2569</v>
       </c>
       <c r="B2570" t="s">
-        <v>2585</v>
+        <v>2584</v>
       </c>
       <c r="C2570" t="s">
-        <v>2582</v>
+        <v>2581</v>
       </c>
     </row>
     <row r="2571" spans="1:3" x14ac:dyDescent="0.3">
@@ -37619,10 +37619,10 @@
         <v>2570</v>
       </c>
       <c r="B2571" t="s">
-        <v>2586</v>
+        <v>2585</v>
       </c>
       <c r="C2571" t="s">
-        <v>2582</v>
+        <v>2581</v>
       </c>
     </row>
     <row r="2572" spans="1:3" x14ac:dyDescent="0.3">
@@ -37630,10 +37630,10 @@
         <v>2571</v>
       </c>
       <c r="B2572" t="s">
+        <v>2586</v>
+      </c>
+      <c r="C2572" t="s">
         <v>2587</v>
-      </c>
-      <c r="C2572" t="s">
-        <v>2588</v>
       </c>
     </row>
     <row r="2573" spans="1:3" x14ac:dyDescent="0.3">
@@ -37641,10 +37641,10 @@
         <v>2572</v>
       </c>
       <c r="B2573" t="s">
-        <v>2589</v>
+        <v>2588</v>
       </c>
       <c r="C2573" t="s">
-        <v>2588</v>
+        <v>2587</v>
       </c>
     </row>
     <row r="2574" spans="1:3" x14ac:dyDescent="0.3">
@@ -37652,10 +37652,10 @@
         <v>2573</v>
       </c>
       <c r="B2574" t="s">
-        <v>2590</v>
+        <v>2589</v>
       </c>
       <c r="C2574" t="s">
-        <v>2588</v>
+        <v>2587</v>
       </c>
     </row>
     <row r="2575" spans="1:3" x14ac:dyDescent="0.3">
@@ -37663,10 +37663,10 @@
         <v>2574</v>
       </c>
       <c r="B2575" t="s">
-        <v>2591</v>
+        <v>2590</v>
       </c>
       <c r="C2575" t="s">
-        <v>2588</v>
+        <v>2587</v>
       </c>
     </row>
     <row r="2576" spans="1:3" x14ac:dyDescent="0.3">
@@ -37674,10 +37674,10 @@
         <v>2575</v>
       </c>
       <c r="B2576" t="s">
-        <v>2592</v>
+        <v>2591</v>
       </c>
       <c r="C2576" t="s">
-        <v>2588</v>
+        <v>2587</v>
       </c>
     </row>
     <row r="2577" spans="1:3" x14ac:dyDescent="0.3">
@@ -37685,10 +37685,10 @@
         <v>2576</v>
       </c>
       <c r="B2577" t="s">
+        <v>2592</v>
+      </c>
+      <c r="C2577" t="s">
         <v>2593</v>
-      </c>
-      <c r="C2577" t="s">
-        <v>2594</v>
       </c>
     </row>
     <row r="2578" spans="1:3" x14ac:dyDescent="0.3">
@@ -37696,10 +37696,10 @@
         <v>2577</v>
       </c>
       <c r="B2578" t="s">
-        <v>2595</v>
+        <v>2594</v>
       </c>
       <c r="C2578" t="s">
-        <v>2594</v>
+        <v>2593</v>
       </c>
     </row>
     <row r="2579" spans="1:3" x14ac:dyDescent="0.3">
@@ -37707,10 +37707,10 @@
         <v>2578</v>
       </c>
       <c r="B2579" t="s">
-        <v>2596</v>
+        <v>2595</v>
       </c>
       <c r="C2579" t="s">
-        <v>2594</v>
+        <v>2593</v>
       </c>
     </row>
     <row r="2580" spans="1:3" x14ac:dyDescent="0.3">
@@ -37718,10 +37718,10 @@
         <v>2579</v>
       </c>
       <c r="B2580" t="s">
-        <v>2597</v>
+        <v>2596</v>
       </c>
       <c r="C2580" t="s">
-        <v>2594</v>
+        <v>2593</v>
       </c>
     </row>
     <row r="2581" spans="1:3" x14ac:dyDescent="0.3">
@@ -37729,10 +37729,10 @@
         <v>2580</v>
       </c>
       <c r="B2581" t="s">
+        <v>2597</v>
+      </c>
+      <c r="C2581" t="s">
         <v>2598</v>
-      </c>
-      <c r="C2581" t="s">
-        <v>2599</v>
       </c>
     </row>
     <row r="2582" spans="1:3" x14ac:dyDescent="0.3">
@@ -37740,10 +37740,10 @@
         <v>2581</v>
       </c>
       <c r="B2582" t="s">
-        <v>2600</v>
+        <v>2599</v>
       </c>
       <c r="C2582" t="s">
-        <v>2599</v>
+        <v>2598</v>
       </c>
     </row>
     <row r="2583" spans="1:3" x14ac:dyDescent="0.3">
@@ -37751,10 +37751,10 @@
         <v>2582</v>
       </c>
       <c r="B2583" t="s">
+        <v>2600</v>
+      </c>
+      <c r="C2583" t="s">
         <v>2601</v>
-      </c>
-      <c r="C2583" t="s">
-        <v>2602</v>
       </c>
     </row>
     <row r="2584" spans="1:3" x14ac:dyDescent="0.3">
@@ -37762,10 +37762,10 @@
         <v>2583</v>
       </c>
       <c r="B2584" t="s">
-        <v>2603</v>
+        <v>2602</v>
       </c>
       <c r="C2584" t="s">
-        <v>2602</v>
+        <v>2601</v>
       </c>
     </row>
     <row r="2585" spans="1:3" x14ac:dyDescent="0.3">
@@ -37773,10 +37773,10 @@
         <v>2584</v>
       </c>
       <c r="B2585" t="s">
+        <v>2603</v>
+      </c>
+      <c r="C2585" t="s">
         <v>2604</v>
-      </c>
-      <c r="C2585" t="s">
-        <v>2605</v>
       </c>
     </row>
     <row r="2586" spans="1:3" x14ac:dyDescent="0.3">
@@ -37784,10 +37784,10 @@
         <v>2585</v>
       </c>
       <c r="B2586" t="s">
-        <v>2606</v>
+        <v>2605</v>
       </c>
       <c r="C2586" t="s">
-        <v>2605</v>
+        <v>2604</v>
       </c>
     </row>
     <row r="2587" spans="1:3" x14ac:dyDescent="0.3">
@@ -37795,10 +37795,10 @@
         <v>2586</v>
       </c>
       <c r="B2587" t="s">
-        <v>2607</v>
+        <v>2606</v>
       </c>
       <c r="C2587" t="s">
-        <v>2605</v>
+        <v>2604</v>
       </c>
     </row>
     <row r="2588" spans="1:3" x14ac:dyDescent="0.3">
@@ -37806,10 +37806,10 @@
         <v>2587</v>
       </c>
       <c r="B2588" t="s">
-        <v>2608</v>
+        <v>2607</v>
       </c>
       <c r="C2588" t="s">
-        <v>2605</v>
+        <v>2604</v>
       </c>
     </row>
     <row r="2589" spans="1:3" x14ac:dyDescent="0.3">
@@ -37817,10 +37817,10 @@
         <v>2588</v>
       </c>
       <c r="B2589" t="s">
-        <v>2609</v>
+        <v>2608</v>
       </c>
       <c r="C2589" t="s">
-        <v>2605</v>
+        <v>2604</v>
       </c>
     </row>
     <row r="2590" spans="1:3" x14ac:dyDescent="0.3">
@@ -37828,10 +37828,10 @@
         <v>2589</v>
       </c>
       <c r="B2590" t="s">
-        <v>2610</v>
+        <v>2609</v>
       </c>
       <c r="C2590" t="s">
-        <v>2605</v>
+        <v>2604</v>
       </c>
     </row>
     <row r="2591" spans="1:3" x14ac:dyDescent="0.3">
@@ -37839,10 +37839,10 @@
         <v>2590</v>
       </c>
       <c r="B2591" t="s">
-        <v>2611</v>
+        <v>2610</v>
       </c>
       <c r="C2591" t="s">
-        <v>2605</v>
+        <v>2604</v>
       </c>
     </row>
     <row r="2592" spans="1:3" x14ac:dyDescent="0.3">
@@ -37850,10 +37850,10 @@
         <v>2591</v>
       </c>
       <c r="B2592" t="s">
-        <v>2612</v>
+        <v>2611</v>
       </c>
       <c r="C2592" t="s">
-        <v>2605</v>
+        <v>2604</v>
       </c>
     </row>
     <row r="2593" spans="1:3" x14ac:dyDescent="0.3">
@@ -37861,10 +37861,10 @@
         <v>2592</v>
       </c>
       <c r="B2593" t="s">
-        <v>2613</v>
+        <v>2612</v>
       </c>
       <c r="C2593" t="s">
-        <v>2605</v>
+        <v>2604</v>
       </c>
     </row>
     <row r="2594" spans="1:3" x14ac:dyDescent="0.3">
@@ -37872,10 +37872,10 @@
         <v>2593</v>
       </c>
       <c r="B2594" t="s">
-        <v>2614</v>
+        <v>2613</v>
       </c>
       <c r="C2594" t="s">
-        <v>2605</v>
+        <v>2604</v>
       </c>
     </row>
     <row r="2595" spans="1:3" x14ac:dyDescent="0.3">
@@ -37883,10 +37883,10 @@
         <v>2594</v>
       </c>
       <c r="B2595" t="s">
-        <v>2615</v>
+        <v>2614</v>
       </c>
       <c r="C2595" t="s">
-        <v>2605</v>
+        <v>2604</v>
       </c>
     </row>
     <row r="2596" spans="1:3" x14ac:dyDescent="0.3">
@@ -37894,10 +37894,10 @@
         <v>2595</v>
       </c>
       <c r="B2596" t="s">
-        <v>2616</v>
+        <v>2615</v>
       </c>
       <c r="C2596" t="s">
-        <v>2605</v>
+        <v>2604</v>
       </c>
     </row>
     <row r="2597" spans="1:3" x14ac:dyDescent="0.3">
@@ -37905,10 +37905,10 @@
         <v>2596</v>
       </c>
       <c r="B2597" t="s">
-        <v>2617</v>
+        <v>2616</v>
       </c>
       <c r="C2597" t="s">
-        <v>2605</v>
+        <v>2604</v>
       </c>
     </row>
     <row r="2598" spans="1:3" x14ac:dyDescent="0.3">
@@ -37916,10 +37916,10 @@
         <v>2597</v>
       </c>
       <c r="B2598" t="s">
-        <v>2618</v>
+        <v>2617</v>
       </c>
       <c r="C2598" t="s">
-        <v>2605</v>
+        <v>2604</v>
       </c>
     </row>
     <row r="2599" spans="1:3" x14ac:dyDescent="0.3">
@@ -37927,10 +37927,10 @@
         <v>2598</v>
       </c>
       <c r="B2599" t="s">
-        <v>2619</v>
+        <v>2618</v>
       </c>
       <c r="C2599" t="s">
-        <v>2605</v>
+        <v>2604</v>
       </c>
     </row>
     <row r="2600" spans="1:3" x14ac:dyDescent="0.3">
@@ -37938,10 +37938,10 @@
         <v>2599</v>
       </c>
       <c r="B2600" t="s">
-        <v>2620</v>
+        <v>2619</v>
       </c>
       <c r="C2600" t="s">
-        <v>2605</v>
+        <v>2604</v>
       </c>
     </row>
     <row r="2601" spans="1:3" x14ac:dyDescent="0.3">
@@ -37949,10 +37949,10 @@
         <v>2600</v>
       </c>
       <c r="B2601" t="s">
-        <v>2621</v>
+        <v>2620</v>
       </c>
       <c r="C2601" t="s">
-        <v>2605</v>
+        <v>2604</v>
       </c>
     </row>
     <row r="2602" spans="1:3" x14ac:dyDescent="0.3">
@@ -37960,10 +37960,10 @@
         <v>2601</v>
       </c>
       <c r="B2602" t="s">
-        <v>2622</v>
+        <v>2621</v>
       </c>
       <c r="C2602" t="s">
-        <v>2605</v>
+        <v>2604</v>
       </c>
     </row>
     <row r="2603" spans="1:3" x14ac:dyDescent="0.3">
@@ -37971,10 +37971,10 @@
         <v>2602</v>
       </c>
       <c r="B2603" t="s">
-        <v>2623</v>
+        <v>2622</v>
       </c>
       <c r="C2603" t="s">
-        <v>2605</v>
+        <v>2604</v>
       </c>
     </row>
     <row r="2604" spans="1:3" x14ac:dyDescent="0.3">
@@ -37982,10 +37982,10 @@
         <v>2603</v>
       </c>
       <c r="B2604" t="s">
-        <v>2624</v>
+        <v>2623</v>
       </c>
       <c r="C2604" t="s">
-        <v>2605</v>
+        <v>2604</v>
       </c>
     </row>
     <row r="2605" spans="1:3" x14ac:dyDescent="0.3">
@@ -37993,10 +37993,10 @@
         <v>2604</v>
       </c>
       <c r="B2605" t="s">
-        <v>2625</v>
+        <v>2624</v>
       </c>
       <c r="C2605" t="s">
-        <v>2605</v>
+        <v>2604</v>
       </c>
     </row>
     <row r="2606" spans="1:3" x14ac:dyDescent="0.3">
@@ -38004,10 +38004,10 @@
         <v>2605</v>
       </c>
       <c r="B2606" t="s">
-        <v>2626</v>
+        <v>2625</v>
       </c>
       <c r="C2606" t="s">
-        <v>2605</v>
+        <v>2604</v>
       </c>
     </row>
     <row r="2607" spans="1:3" x14ac:dyDescent="0.3">
@@ -38015,10 +38015,10 @@
         <v>2606</v>
       </c>
       <c r="B2607" t="s">
-        <v>2627</v>
+        <v>2626</v>
       </c>
       <c r="C2607" t="s">
-        <v>2605</v>
+        <v>2604</v>
       </c>
     </row>
     <row r="2608" spans="1:3" x14ac:dyDescent="0.3">
@@ -38026,10 +38026,10 @@
         <v>2607</v>
       </c>
       <c r="B2608" t="s">
-        <v>2628</v>
+        <v>2627</v>
       </c>
       <c r="C2608" t="s">
-        <v>2605</v>
+        <v>2604</v>
       </c>
     </row>
     <row r="2609" spans="1:3" x14ac:dyDescent="0.3">
@@ -38037,10 +38037,10 @@
         <v>2608</v>
       </c>
       <c r="B2609" t="s">
-        <v>2629</v>
+        <v>2628</v>
       </c>
       <c r="C2609" t="s">
-        <v>2605</v>
+        <v>2604</v>
       </c>
     </row>
     <row r="2610" spans="1:3" x14ac:dyDescent="0.3">
@@ -38048,10 +38048,10 @@
         <v>2609</v>
       </c>
       <c r="B2610" t="s">
-        <v>2630</v>
+        <v>2629</v>
       </c>
       <c r="C2610" t="s">
-        <v>2605</v>
+        <v>2604</v>
       </c>
     </row>
     <row r="2611" spans="1:3" x14ac:dyDescent="0.3">
@@ -38059,10 +38059,10 @@
         <v>2610</v>
       </c>
       <c r="B2611" t="s">
-        <v>2631</v>
+        <v>2630</v>
       </c>
       <c r="C2611" t="s">
-        <v>2605</v>
+        <v>2604</v>
       </c>
     </row>
     <row r="2612" spans="1:3" x14ac:dyDescent="0.3">
@@ -38070,10 +38070,10 @@
         <v>2611</v>
       </c>
       <c r="B2612" t="s">
-        <v>2632</v>
+        <v>2631</v>
       </c>
       <c r="C2612" t="s">
-        <v>2605</v>
+        <v>2604</v>
       </c>
     </row>
     <row r="2613" spans="1:3" x14ac:dyDescent="0.3">
@@ -38081,10 +38081,10 @@
         <v>2612</v>
       </c>
       <c r="B2613" t="s">
-        <v>2633</v>
+        <v>2632</v>
       </c>
       <c r="C2613" t="s">
-        <v>2605</v>
+        <v>2604</v>
       </c>
     </row>
     <row r="2614" spans="1:3" x14ac:dyDescent="0.3">
@@ -38092,10 +38092,10 @@
         <v>2613</v>
       </c>
       <c r="B2614" t="s">
-        <v>2634</v>
+        <v>2633</v>
       </c>
       <c r="C2614" t="s">
-        <v>2605</v>
+        <v>2604</v>
       </c>
     </row>
     <row r="2615" spans="1:3" x14ac:dyDescent="0.3">
@@ -38103,10 +38103,10 @@
         <v>2614</v>
       </c>
       <c r="B2615" t="s">
-        <v>2635</v>
+        <v>2634</v>
       </c>
       <c r="C2615" t="s">
-        <v>2605</v>
+        <v>2604</v>
       </c>
     </row>
     <row r="2616" spans="1:3" x14ac:dyDescent="0.3">
@@ -38114,10 +38114,10 @@
         <v>2615</v>
       </c>
       <c r="B2616" t="s">
-        <v>2636</v>
+        <v>2635</v>
       </c>
       <c r="C2616" t="s">
-        <v>2605</v>
+        <v>2604</v>
       </c>
     </row>
     <row r="2617" spans="1:3" x14ac:dyDescent="0.3">
@@ -38125,10 +38125,10 @@
         <v>2616</v>
       </c>
       <c r="B2617" t="s">
-        <v>2637</v>
+        <v>2636</v>
       </c>
       <c r="C2617" t="s">
-        <v>2605</v>
+        <v>2604</v>
       </c>
     </row>
     <row r="2618" spans="1:3" x14ac:dyDescent="0.3">
@@ -38136,10 +38136,10 @@
         <v>2617</v>
       </c>
       <c r="B2618" t="s">
-        <v>2638</v>
+        <v>2637</v>
       </c>
       <c r="C2618" t="s">
-        <v>2605</v>
+        <v>2604</v>
       </c>
     </row>
     <row r="2619" spans="1:3" x14ac:dyDescent="0.3">
@@ -38147,10 +38147,10 @@
         <v>2618</v>
       </c>
       <c r="B2619" t="s">
-        <v>2639</v>
+        <v>2638</v>
       </c>
       <c r="C2619" t="s">
-        <v>2605</v>
+        <v>2604</v>
       </c>
     </row>
     <row r="2620" spans="1:3" x14ac:dyDescent="0.3">
@@ -38158,10 +38158,10 @@
         <v>2619</v>
       </c>
       <c r="B2620" t="s">
-        <v>2640</v>
+        <v>2639</v>
       </c>
       <c r="C2620" t="s">
-        <v>2605</v>
+        <v>2604</v>
       </c>
     </row>
     <row r="2621" spans="1:3" x14ac:dyDescent="0.3">
@@ -38169,10 +38169,10 @@
         <v>2620</v>
       </c>
       <c r="B2621" t="s">
-        <v>2641</v>
+        <v>2640</v>
       </c>
       <c r="C2621" t="s">
-        <v>2605</v>
+        <v>2604</v>
       </c>
     </row>
     <row r="2622" spans="1:3" x14ac:dyDescent="0.3">
@@ -38180,10 +38180,10 @@
         <v>2621</v>
       </c>
       <c r="B2622" t="s">
-        <v>2642</v>
+        <v>2641</v>
       </c>
       <c r="C2622" t="s">
-        <v>2605</v>
+        <v>2604</v>
       </c>
     </row>
     <row r="2623" spans="1:3" x14ac:dyDescent="0.3">
@@ -38191,10 +38191,10 @@
         <v>2622</v>
       </c>
       <c r="B2623" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
       <c r="C2623" t="s">
-        <v>2605</v>
+        <v>2604</v>
       </c>
     </row>
     <row r="2624" spans="1:3" x14ac:dyDescent="0.3">
@@ -38202,10 +38202,10 @@
         <v>2623</v>
       </c>
       <c r="B2624" t="s">
-        <v>2644</v>
+        <v>2643</v>
       </c>
       <c r="C2624" t="s">
-        <v>2605</v>
+        <v>2604</v>
       </c>
     </row>
     <row r="2625" spans="1:3" x14ac:dyDescent="0.3">
@@ -38213,10 +38213,10 @@
         <v>2624</v>
       </c>
       <c r="B2625" t="s">
-        <v>2645</v>
+        <v>2644</v>
       </c>
       <c r="C2625" t="s">
-        <v>2605</v>
+        <v>2604</v>
       </c>
     </row>
     <row r="2626" spans="1:3" x14ac:dyDescent="0.3">
@@ -38224,10 +38224,10 @@
         <v>2625</v>
       </c>
       <c r="B2626" t="s">
-        <v>2646</v>
+        <v>2645</v>
       </c>
       <c r="C2626" t="s">
-        <v>2605</v>
+        <v>2604</v>
       </c>
     </row>
     <row r="2627" spans="1:3" x14ac:dyDescent="0.3">
@@ -38235,10 +38235,10 @@
         <v>2626</v>
       </c>
       <c r="B2627" t="s">
-        <v>2647</v>
+        <v>2646</v>
       </c>
       <c r="C2627" t="s">
-        <v>2605</v>
+        <v>2604</v>
       </c>
     </row>
     <row r="2628" spans="1:3" x14ac:dyDescent="0.3">
@@ -38246,10 +38246,10 @@
         <v>2627</v>
       </c>
       <c r="B2628" t="s">
-        <v>2648</v>
+        <v>2647</v>
       </c>
       <c r="C2628" t="s">
-        <v>2605</v>
+        <v>2604</v>
       </c>
     </row>
     <row r="2629" spans="1:3" x14ac:dyDescent="0.3">
@@ -38257,10 +38257,10 @@
         <v>2628</v>
       </c>
       <c r="B2629" t="s">
-        <v>2649</v>
+        <v>2648</v>
       </c>
       <c r="C2629" t="s">
-        <v>2605</v>
+        <v>2604</v>
       </c>
     </row>
     <row r="2630" spans="1:3" x14ac:dyDescent="0.3">
@@ -38268,10 +38268,10 @@
         <v>2629</v>
       </c>
       <c r="B2630" t="s">
-        <v>2650</v>
+        <v>2649</v>
       </c>
       <c r="C2630" t="s">
-        <v>2605</v>
+        <v>2604</v>
       </c>
     </row>
     <row r="2631" spans="1:3" x14ac:dyDescent="0.3">
@@ -38279,10 +38279,10 @@
         <v>2630</v>
       </c>
       <c r="B2631" t="s">
-        <v>2651</v>
+        <v>2650</v>
       </c>
       <c r="C2631" t="s">
-        <v>2605</v>
+        <v>2604</v>
       </c>
     </row>
     <row r="2632" spans="1:3" x14ac:dyDescent="0.3">
@@ -38290,10 +38290,10 @@
         <v>2631</v>
       </c>
       <c r="B2632" t="s">
-        <v>2652</v>
+        <v>2651</v>
       </c>
       <c r="C2632" t="s">
-        <v>2605</v>
+        <v>2604</v>
       </c>
     </row>
     <row r="2633" spans="1:3" x14ac:dyDescent="0.3">
@@ -38301,10 +38301,10 @@
         <v>2632</v>
       </c>
       <c r="B2633" t="s">
-        <v>2653</v>
+        <v>2652</v>
       </c>
       <c r="C2633" t="s">
-        <v>2605</v>
+        <v>2604</v>
       </c>
     </row>
     <row r="2634" spans="1:3" x14ac:dyDescent="0.3">
@@ -38312,10 +38312,10 @@
         <v>2633</v>
       </c>
       <c r="B2634" t="s">
-        <v>2654</v>
+        <v>2653</v>
       </c>
       <c r="C2634" t="s">
-        <v>2605</v>
+        <v>2604</v>
       </c>
     </row>
     <row r="2635" spans="1:3" x14ac:dyDescent="0.3">
@@ -38323,10 +38323,10 @@
         <v>2634</v>
       </c>
       <c r="B2635" t="s">
-        <v>2655</v>
+        <v>2654</v>
       </c>
       <c r="C2635" t="s">
-        <v>2605</v>
+        <v>2604</v>
       </c>
     </row>
     <row r="2636" spans="1:3" x14ac:dyDescent="0.3">
@@ -38334,10 +38334,10 @@
         <v>2635</v>
       </c>
       <c r="B2636" t="s">
-        <v>2656</v>
+        <v>2655</v>
       </c>
       <c r="C2636" t="s">
-        <v>2605</v>
+        <v>2604</v>
       </c>
     </row>
     <row r="2637" spans="1:3" x14ac:dyDescent="0.3">
@@ -38345,10 +38345,10 @@
         <v>2636</v>
       </c>
       <c r="B2637" t="s">
-        <v>2657</v>
+        <v>2656</v>
       </c>
       <c r="C2637" t="s">
-        <v>2605</v>
+        <v>2604</v>
       </c>
     </row>
     <row r="2638" spans="1:3" x14ac:dyDescent="0.3">
@@ -38356,10 +38356,10 @@
         <v>2637</v>
       </c>
       <c r="B2638" t="s">
-        <v>2658</v>
+        <v>2657</v>
       </c>
       <c r="C2638" t="s">
-        <v>2605</v>
+        <v>2604</v>
       </c>
     </row>
     <row r="2639" spans="1:3" x14ac:dyDescent="0.3">
@@ -38367,10 +38367,10 @@
         <v>2638</v>
       </c>
       <c r="B2639" t="s">
-        <v>2659</v>
+        <v>2658</v>
       </c>
       <c r="C2639" t="s">
-        <v>2605</v>
+        <v>2604</v>
       </c>
     </row>
     <row r="2640" spans="1:3" x14ac:dyDescent="0.3">
@@ -38378,10 +38378,10 @@
         <v>2639</v>
       </c>
       <c r="B2640" t="s">
-        <v>2660</v>
+        <v>2659</v>
       </c>
       <c r="C2640" t="s">
-        <v>2605</v>
+        <v>2604</v>
       </c>
     </row>
     <row r="2641" spans="1:3" x14ac:dyDescent="0.3">
@@ -38389,10 +38389,10 @@
         <v>2640</v>
       </c>
       <c r="B2641" t="s">
-        <v>2661</v>
+        <v>2660</v>
       </c>
       <c r="C2641" t="s">
-        <v>2605</v>
+        <v>2604</v>
       </c>
     </row>
     <row r="2642" spans="1:3" x14ac:dyDescent="0.3">
@@ -38400,10 +38400,10 @@
         <v>2641</v>
       </c>
       <c r="B2642" t="s">
-        <v>2662</v>
+        <v>2661</v>
       </c>
       <c r="C2642" t="s">
-        <v>2605</v>
+        <v>2604</v>
       </c>
     </row>
     <row r="2643" spans="1:3" x14ac:dyDescent="0.3">
@@ -38411,10 +38411,10 @@
         <v>2642</v>
       </c>
       <c r="B2643" t="s">
-        <v>2663</v>
+        <v>2662</v>
       </c>
       <c r="C2643" t="s">
-        <v>2605</v>
+        <v>2604</v>
       </c>
     </row>
     <row r="2644" spans="1:3" x14ac:dyDescent="0.3">
@@ -38422,10 +38422,10 @@
         <v>2643</v>
       </c>
       <c r="B2644" t="s">
-        <v>2664</v>
+        <v>2663</v>
       </c>
       <c r="C2644" t="s">
-        <v>2605</v>
+        <v>2604</v>
       </c>
     </row>
     <row r="2645" spans="1:3" x14ac:dyDescent="0.3">
@@ -38433,10 +38433,10 @@
         <v>2644</v>
       </c>
       <c r="B2645" t="s">
-        <v>2665</v>
+        <v>2664</v>
       </c>
       <c r="C2645" t="s">
-        <v>2605</v>
+        <v>2604</v>
       </c>
     </row>
     <row r="2646" spans="1:3" x14ac:dyDescent="0.3">
@@ -38444,10 +38444,10 @@
         <v>2645</v>
       </c>
       <c r="B2646" t="s">
-        <v>2666</v>
+        <v>2665</v>
       </c>
       <c r="C2646" t="s">
-        <v>2605</v>
+        <v>2604</v>
       </c>
     </row>
     <row r="2647" spans="1:3" x14ac:dyDescent="0.3">
@@ -38455,10 +38455,10 @@
         <v>2646</v>
       </c>
       <c r="B2647" t="s">
-        <v>2667</v>
+        <v>2666</v>
       </c>
       <c r="C2647" t="s">
-        <v>2605</v>
+        <v>2604</v>
       </c>
     </row>
     <row r="2648" spans="1:3" x14ac:dyDescent="0.3">
@@ -38466,10 +38466,10 @@
         <v>2647</v>
       </c>
       <c r="B2648" t="s">
-        <v>2668</v>
+        <v>2667</v>
       </c>
       <c r="C2648" t="s">
-        <v>2605</v>
+        <v>2604</v>
       </c>
     </row>
     <row r="2649" spans="1:3" x14ac:dyDescent="0.3">
@@ -38477,10 +38477,10 @@
         <v>2648</v>
       </c>
       <c r="B2649" t="s">
-        <v>2669</v>
+        <v>2668</v>
       </c>
       <c r="C2649" t="s">
-        <v>2605</v>
+        <v>2604</v>
       </c>
     </row>
     <row r="2650" spans="1:3" x14ac:dyDescent="0.3">
@@ -38488,10 +38488,10 @@
         <v>2649</v>
       </c>
       <c r="B2650" t="s">
-        <v>2670</v>
+        <v>2669</v>
       </c>
       <c r="C2650" t="s">
-        <v>2605</v>
+        <v>2604</v>
       </c>
     </row>
     <row r="2651" spans="1:3" x14ac:dyDescent="0.3">
@@ -38499,10 +38499,10 @@
         <v>2650</v>
       </c>
       <c r="B2651" t="s">
-        <v>2671</v>
+        <v>2670</v>
       </c>
       <c r="C2651" t="s">
-        <v>2605</v>
+        <v>2604</v>
       </c>
     </row>
     <row r="2652" spans="1:3" x14ac:dyDescent="0.3">
@@ -38510,10 +38510,10 @@
         <v>2651</v>
       </c>
       <c r="B2652" t="s">
-        <v>2672</v>
+        <v>2671</v>
       </c>
       <c r="C2652" t="s">
-        <v>2605</v>
+        <v>2604</v>
       </c>
     </row>
     <row r="2653" spans="1:3" x14ac:dyDescent="0.3">
@@ -38521,10 +38521,10 @@
         <v>2652</v>
       </c>
       <c r="B2653" t="s">
-        <v>2673</v>
+        <v>2672</v>
       </c>
       <c r="C2653" t="s">
-        <v>2605</v>
+        <v>2604</v>
       </c>
     </row>
     <row r="2654" spans="1:3" x14ac:dyDescent="0.3">
@@ -38532,10 +38532,10 @@
         <v>2653</v>
       </c>
       <c r="B2654" t="s">
-        <v>2674</v>
+        <v>2673</v>
       </c>
       <c r="C2654" t="s">
-        <v>2605</v>
+        <v>2604</v>
       </c>
     </row>
     <row r="2655" spans="1:3" x14ac:dyDescent="0.3">
@@ -38543,10 +38543,10 @@
         <v>2654</v>
       </c>
       <c r="B2655" t="s">
-        <v>2675</v>
+        <v>2674</v>
       </c>
       <c r="C2655" t="s">
-        <v>2605</v>
+        <v>2604</v>
       </c>
     </row>
     <row r="2656" spans="1:3" x14ac:dyDescent="0.3">
@@ -38554,10 +38554,10 @@
         <v>2655</v>
       </c>
       <c r="B2656" t="s">
-        <v>2676</v>
+        <v>2675</v>
       </c>
       <c r="C2656" t="s">
-        <v>2605</v>
+        <v>2604</v>
       </c>
     </row>
     <row r="2657" spans="1:3" x14ac:dyDescent="0.3">
@@ -38565,10 +38565,10 @@
         <v>2656</v>
       </c>
       <c r="B2657" t="s">
-        <v>2677</v>
+        <v>2676</v>
       </c>
       <c r="C2657" t="s">
-        <v>2605</v>
+        <v>2604</v>
       </c>
     </row>
     <row r="2658" spans="1:3" x14ac:dyDescent="0.3">
@@ -38576,10 +38576,10 @@
         <v>2657</v>
       </c>
       <c r="B2658" t="s">
-        <v>2678</v>
+        <v>2677</v>
       </c>
       <c r="C2658" t="s">
-        <v>2605</v>
+        <v>2604</v>
       </c>
     </row>
     <row r="2659" spans="1:3" x14ac:dyDescent="0.3">
@@ -38587,10 +38587,10 @@
         <v>2658</v>
       </c>
       <c r="B2659" t="s">
-        <v>2679</v>
+        <v>2678</v>
       </c>
       <c r="C2659" t="s">
-        <v>2605</v>
+        <v>2604</v>
       </c>
     </row>
     <row r="2660" spans="1:3" x14ac:dyDescent="0.3">
@@ -38598,10 +38598,10 @@
         <v>2659</v>
       </c>
       <c r="B2660" t="s">
-        <v>2680</v>
+        <v>2679</v>
       </c>
       <c r="C2660" t="s">
-        <v>2605</v>
+        <v>2604</v>
       </c>
     </row>
     <row r="2661" spans="1:3" x14ac:dyDescent="0.3">
@@ -38609,10 +38609,10 @@
         <v>2660</v>
       </c>
       <c r="B2661" t="s">
-        <v>2681</v>
+        <v>2680</v>
       </c>
       <c r="C2661" t="s">
-        <v>2605</v>
+        <v>2604</v>
       </c>
     </row>
     <row r="2662" spans="1:3" x14ac:dyDescent="0.3">
@@ -38620,10 +38620,10 @@
         <v>2661</v>
       </c>
       <c r="B2662" t="s">
-        <v>2682</v>
+        <v>2681</v>
       </c>
       <c r="C2662" t="s">
-        <v>2605</v>
+        <v>2604</v>
       </c>
     </row>
     <row r="2663" spans="1:3" x14ac:dyDescent="0.3">
@@ -38631,10 +38631,10 @@
         <v>2662</v>
       </c>
       <c r="B2663" t="s">
-        <v>2683</v>
+        <v>2682</v>
       </c>
       <c r="C2663" t="s">
-        <v>2605</v>
+        <v>2604</v>
       </c>
     </row>
     <row r="2664" spans="1:3" x14ac:dyDescent="0.3">
@@ -38642,10 +38642,10 @@
         <v>2663</v>
       </c>
       <c r="B2664" t="s">
-        <v>2684</v>
+        <v>2683</v>
       </c>
       <c r="C2664" t="s">
-        <v>2605</v>
+        <v>2604</v>
       </c>
     </row>
     <row r="2665" spans="1:3" x14ac:dyDescent="0.3">
@@ -38653,10 +38653,10 @@
         <v>2664</v>
       </c>
       <c r="B2665" t="s">
-        <v>2685</v>
+        <v>2684</v>
       </c>
       <c r="C2665" t="s">
-        <v>2605</v>
+        <v>2604</v>
       </c>
     </row>
     <row r="2666" spans="1:3" x14ac:dyDescent="0.3">
@@ -38664,10 +38664,10 @@
         <v>2665</v>
       </c>
       <c r="B2666" t="s">
-        <v>2686</v>
+        <v>2685</v>
       </c>
       <c r="C2666" t="s">
-        <v>2605</v>
+        <v>2604</v>
       </c>
     </row>
     <row r="2667" spans="1:3" x14ac:dyDescent="0.3">
@@ -38675,10 +38675,10 @@
         <v>2666</v>
       </c>
       <c r="B2667" t="s">
-        <v>2687</v>
+        <v>2686</v>
       </c>
       <c r="C2667" t="s">
-        <v>2605</v>
+        <v>2604</v>
       </c>
     </row>
     <row r="2668" spans="1:3" x14ac:dyDescent="0.3">
@@ -38686,10 +38686,10 @@
         <v>2667</v>
       </c>
       <c r="B2668" t="s">
-        <v>2688</v>
+        <v>2687</v>
       </c>
       <c r="C2668" t="s">
-        <v>2605</v>
+        <v>2604</v>
       </c>
     </row>
     <row r="2669" spans="1:3" x14ac:dyDescent="0.3">
@@ -38697,10 +38697,10 @@
         <v>2668</v>
       </c>
       <c r="B2669" t="s">
-        <v>2689</v>
+        <v>2688</v>
       </c>
       <c r="C2669" t="s">
-        <v>2605</v>
+        <v>2604</v>
       </c>
     </row>
     <row r="2670" spans="1:3" x14ac:dyDescent="0.3">
@@ -38708,10 +38708,10 @@
         <v>2669</v>
       </c>
       <c r="B2670" t="s">
-        <v>2690</v>
+        <v>2689</v>
       </c>
       <c r="C2670" t="s">
-        <v>2605</v>
+        <v>2604</v>
       </c>
     </row>
     <row r="2671" spans="1:3" x14ac:dyDescent="0.3">
@@ -38719,10 +38719,10 @@
         <v>2670</v>
       </c>
       <c r="B2671" t="s">
-        <v>2691</v>
+        <v>2690</v>
       </c>
       <c r="C2671" t="s">
-        <v>2605</v>
+        <v>2604</v>
       </c>
     </row>
     <row r="2672" spans="1:3" x14ac:dyDescent="0.3">
@@ -38730,10 +38730,10 @@
         <v>2671</v>
       </c>
       <c r="B2672" t="s">
-        <v>2692</v>
+        <v>2691</v>
       </c>
       <c r="C2672" t="s">
-        <v>2605</v>
+        <v>2604</v>
       </c>
     </row>
     <row r="2673" spans="1:3" x14ac:dyDescent="0.3">
@@ -38741,10 +38741,10 @@
         <v>2672</v>
       </c>
       <c r="B2673" t="s">
-        <v>2693</v>
+        <v>2692</v>
       </c>
       <c r="C2673" t="s">
-        <v>2605</v>
+        <v>2604</v>
       </c>
     </row>
     <row r="2674" spans="1:3" x14ac:dyDescent="0.3">
@@ -38752,10 +38752,10 @@
         <v>2673</v>
       </c>
       <c r="B2674" t="s">
+        <v>2693</v>
+      </c>
+      <c r="C2674" t="s">
         <v>2694</v>
-      </c>
-      <c r="C2674" t="s">
-        <v>2695</v>
       </c>
     </row>
     <row r="2675" spans="1:3" x14ac:dyDescent="0.3">
@@ -38763,10 +38763,10 @@
         <v>2674</v>
       </c>
       <c r="B2675" t="s">
-        <v>2696</v>
+        <v>2695</v>
       </c>
       <c r="C2675" t="s">
-        <v>2695</v>
+        <v>2694</v>
       </c>
     </row>
     <row r="2676" spans="1:3" x14ac:dyDescent="0.3">
@@ -38774,10 +38774,10 @@
         <v>2675</v>
       </c>
       <c r="B2676" t="s">
-        <v>2697</v>
+        <v>2696</v>
       </c>
       <c r="C2676" t="s">
-        <v>2695</v>
+        <v>2694</v>
       </c>
     </row>
     <row r="2677" spans="1:3" x14ac:dyDescent="0.3">
@@ -38785,10 +38785,10 @@
         <v>2676</v>
       </c>
       <c r="B2677" t="s">
-        <v>2698</v>
+        <v>2697</v>
       </c>
       <c r="C2677" t="s">
-        <v>2695</v>
+        <v>2694</v>
       </c>
     </row>
     <row r="2678" spans="1:3" x14ac:dyDescent="0.3">
@@ -38796,10 +38796,10 @@
         <v>2677</v>
       </c>
       <c r="B2678" t="s">
-        <v>2699</v>
+        <v>2698</v>
       </c>
       <c r="C2678" t="s">
-        <v>2695</v>
+        <v>2694</v>
       </c>
     </row>
     <row r="2679" spans="1:3" x14ac:dyDescent="0.3">
@@ -38807,10 +38807,10 @@
         <v>2678</v>
       </c>
       <c r="B2679" t="s">
-        <v>2700</v>
+        <v>2699</v>
       </c>
       <c r="C2679" t="s">
-        <v>2695</v>
+        <v>2694</v>
       </c>
     </row>
     <row r="2680" spans="1:3" x14ac:dyDescent="0.3">
@@ -38818,10 +38818,10 @@
         <v>2679</v>
       </c>
       <c r="B2680" t="s">
-        <v>2701</v>
+        <v>2700</v>
       </c>
       <c r="C2680" t="s">
-        <v>2695</v>
+        <v>2694</v>
       </c>
     </row>
     <row r="2681" spans="1:3" x14ac:dyDescent="0.3">
@@ -38829,10 +38829,10 @@
         <v>2680</v>
       </c>
       <c r="B2681" t="s">
-        <v>2702</v>
+        <v>2701</v>
       </c>
       <c r="C2681" t="s">
-        <v>2695</v>
+        <v>2694</v>
       </c>
     </row>
     <row r="2682" spans="1:3" x14ac:dyDescent="0.3">
@@ -38840,10 +38840,10 @@
         <v>2681</v>
       </c>
       <c r="B2682" t="s">
-        <v>2703</v>
+        <v>2702</v>
       </c>
       <c r="C2682" t="s">
-        <v>2695</v>
+        <v>2694</v>
       </c>
     </row>
     <row r="2683" spans="1:3" x14ac:dyDescent="0.3">
@@ -38851,10 +38851,10 @@
         <v>2682</v>
       </c>
       <c r="B2683" t="s">
-        <v>2704</v>
+        <v>2703</v>
       </c>
       <c r="C2683" t="s">
-        <v>2695</v>
+        <v>2694</v>
       </c>
     </row>
     <row r="2684" spans="1:3" x14ac:dyDescent="0.3">
@@ -38862,10 +38862,10 @@
         <v>2683</v>
       </c>
       <c r="B2684" t="s">
-        <v>2705</v>
+        <v>2704</v>
       </c>
       <c r="C2684" t="s">
-        <v>2695</v>
+        <v>2694</v>
       </c>
     </row>
     <row r="2685" spans="1:3" x14ac:dyDescent="0.3">
@@ -38873,10 +38873,10 @@
         <v>2684</v>
       </c>
       <c r="B2685" t="s">
-        <v>2706</v>
+        <v>2705</v>
       </c>
       <c r="C2685" t="s">
-        <v>2695</v>
+        <v>2694</v>
       </c>
     </row>
     <row r="2686" spans="1:3" x14ac:dyDescent="0.3">
@@ -38884,10 +38884,10 @@
         <v>2685</v>
       </c>
       <c r="B2686" t="s">
-        <v>2707</v>
+        <v>2706</v>
       </c>
       <c r="C2686" t="s">
-        <v>2695</v>
+        <v>2694</v>
       </c>
     </row>
     <row r="2687" spans="1:3" x14ac:dyDescent="0.3">
@@ -38895,10 +38895,10 @@
         <v>2686</v>
       </c>
       <c r="B2687" t="s">
-        <v>2708</v>
+        <v>2707</v>
       </c>
       <c r="C2687" t="s">
-        <v>2695</v>
+        <v>2694</v>
       </c>
     </row>
     <row r="2688" spans="1:3" x14ac:dyDescent="0.3">
@@ -38906,10 +38906,10 @@
         <v>2687</v>
       </c>
       <c r="B2688" t="s">
-        <v>2709</v>
+        <v>2708</v>
       </c>
       <c r="C2688" t="s">
-        <v>2695</v>
+        <v>2694</v>
       </c>
     </row>
     <row r="2689" spans="1:3" x14ac:dyDescent="0.3">
@@ -38917,10 +38917,10 @@
         <v>2688</v>
       </c>
       <c r="B2689" t="s">
-        <v>2710</v>
+        <v>2709</v>
       </c>
       <c r="C2689" t="s">
-        <v>2695</v>
+        <v>2694</v>
       </c>
     </row>
     <row r="2690" spans="1:3" x14ac:dyDescent="0.3">
@@ -38928,10 +38928,10 @@
         <v>2689</v>
       </c>
       <c r="B2690" t="s">
-        <v>2711</v>
+        <v>2710</v>
       </c>
       <c r="C2690" t="s">
-        <v>2695</v>
+        <v>2694</v>
       </c>
     </row>
     <row r="2691" spans="1:3" x14ac:dyDescent="0.3">
@@ -38939,10 +38939,10 @@
         <v>2690</v>
       </c>
       <c r="B2691" t="s">
-        <v>2712</v>
+        <v>2711</v>
       </c>
       <c r="C2691" t="s">
-        <v>2695</v>
+        <v>2694</v>
       </c>
     </row>
     <row r="2692" spans="1:3" x14ac:dyDescent="0.3">
@@ -38950,10 +38950,10 @@
         <v>2691</v>
       </c>
       <c r="B2692" t="s">
-        <v>2713</v>
+        <v>2712</v>
       </c>
       <c r="C2692" t="s">
-        <v>2695</v>
+        <v>2694</v>
       </c>
     </row>
     <row r="2693" spans="1:3" x14ac:dyDescent="0.3">
@@ -38961,10 +38961,10 @@
         <v>2692</v>
       </c>
       <c r="B2693" t="s">
-        <v>2714</v>
+        <v>2713</v>
       </c>
       <c r="C2693" t="s">
-        <v>2695</v>
+        <v>2694</v>
       </c>
     </row>
     <row r="2694" spans="1:3" x14ac:dyDescent="0.3">
@@ -38972,10 +38972,10 @@
         <v>2693</v>
       </c>
       <c r="B2694" t="s">
-        <v>2715</v>
+        <v>2714</v>
       </c>
       <c r="C2694" t="s">
-        <v>2695</v>
+        <v>2694</v>
       </c>
     </row>
     <row r="2695" spans="1:3" x14ac:dyDescent="0.3">
@@ -38983,10 +38983,10 @@
         <v>2694</v>
       </c>
       <c r="B2695" t="s">
-        <v>2716</v>
+        <v>2715</v>
       </c>
       <c r="C2695" t="s">
-        <v>2695</v>
+        <v>2694</v>
       </c>
     </row>
     <row r="2696" spans="1:3" x14ac:dyDescent="0.3">
@@ -38994,10 +38994,10 @@
         <v>2695</v>
       </c>
       <c r="B2696" t="s">
-        <v>2717</v>
+        <v>2716</v>
       </c>
       <c r="C2696" t="s">
-        <v>2695</v>
+        <v>2694</v>
       </c>
     </row>
     <row r="2697" spans="1:3" x14ac:dyDescent="0.3">
@@ -39005,10 +39005,10 @@
         <v>2696</v>
       </c>
       <c r="B2697" t="s">
+        <v>2717</v>
+      </c>
+      <c r="C2697" t="s">
         <v>2718</v>
-      </c>
-      <c r="C2697" t="s">
-        <v>2719</v>
       </c>
     </row>
     <row r="2698" spans="1:3" x14ac:dyDescent="0.3">
@@ -39016,10 +39016,10 @@
         <v>2697</v>
       </c>
       <c r="B2698" t="s">
-        <v>2720</v>
+        <v>2719</v>
       </c>
       <c r="C2698" t="s">
-        <v>2719</v>
+        <v>2718</v>
       </c>
     </row>
     <row r="2699" spans="1:3" x14ac:dyDescent="0.3">
@@ -39027,10 +39027,10 @@
         <v>2698</v>
       </c>
       <c r="B2699" t="s">
-        <v>2721</v>
+        <v>2720</v>
       </c>
       <c r="C2699" t="s">
-        <v>2719</v>
+        <v>2718</v>
       </c>
     </row>
     <row r="2700" spans="1:3" x14ac:dyDescent="0.3">
@@ -39038,10 +39038,10 @@
         <v>2699</v>
       </c>
       <c r="B2700" t="s">
-        <v>2722</v>
+        <v>2721</v>
       </c>
       <c r="C2700" t="s">
-        <v>2719</v>
+        <v>2718</v>
       </c>
     </row>
     <row r="2701" spans="1:3" x14ac:dyDescent="0.3">
@@ -39049,10 +39049,10 @@
         <v>2700</v>
       </c>
       <c r="B2701" t="s">
-        <v>2723</v>
+        <v>2722</v>
       </c>
       <c r="C2701" t="s">
-        <v>2719</v>
+        <v>2718</v>
       </c>
     </row>
     <row r="2702" spans="1:3" x14ac:dyDescent="0.3">
@@ -39060,10 +39060,10 @@
         <v>2701</v>
       </c>
       <c r="B2702" t="s">
-        <v>2724</v>
+        <v>2723</v>
       </c>
       <c r="C2702" t="s">
-        <v>2719</v>
+        <v>2718</v>
       </c>
     </row>
     <row r="2703" spans="1:3" x14ac:dyDescent="0.3">
@@ -39071,10 +39071,10 @@
         <v>2702</v>
       </c>
       <c r="B2703" t="s">
-        <v>2725</v>
+        <v>2724</v>
       </c>
       <c r="C2703" t="s">
-        <v>2719</v>
+        <v>2718</v>
       </c>
     </row>
     <row r="2704" spans="1:3" x14ac:dyDescent="0.3">
@@ -39082,10 +39082,10 @@
         <v>2703</v>
       </c>
       <c r="B2704" t="s">
-        <v>2726</v>
+        <v>2725</v>
       </c>
       <c r="C2704" t="s">
-        <v>2719</v>
+        <v>2718</v>
       </c>
     </row>
     <row r="2705" spans="1:3" x14ac:dyDescent="0.3">
@@ -39093,10 +39093,10 @@
         <v>2704</v>
       </c>
       <c r="B2705" t="s">
-        <v>2727</v>
+        <v>2726</v>
       </c>
       <c r="C2705" t="s">
-        <v>2719</v>
+        <v>2718</v>
       </c>
     </row>
     <row r="2706" spans="1:3" x14ac:dyDescent="0.3">
@@ -39104,10 +39104,10 @@
         <v>2705</v>
       </c>
       <c r="B2706" t="s">
-        <v>2728</v>
+        <v>2727</v>
       </c>
       <c r="C2706" t="s">
-        <v>2719</v>
+        <v>2718</v>
       </c>
     </row>
     <row r="2707" spans="1:3" x14ac:dyDescent="0.3">
@@ -39115,10 +39115,10 @@
         <v>2706</v>
       </c>
       <c r="B2707" t="s">
-        <v>2729</v>
+        <v>2728</v>
       </c>
       <c r="C2707" t="s">
-        <v>2719</v>
+        <v>2718</v>
       </c>
     </row>
     <row r="2708" spans="1:3" x14ac:dyDescent="0.3">
@@ -39126,10 +39126,10 @@
         <v>2707</v>
       </c>
       <c r="B2708" t="s">
-        <v>2730</v>
+        <v>2729</v>
       </c>
       <c r="C2708" t="s">
-        <v>2719</v>
+        <v>2718</v>
       </c>
     </row>
     <row r="2709" spans="1:3" x14ac:dyDescent="0.3">
@@ -39137,10 +39137,10 @@
         <v>2708</v>
       </c>
       <c r="B2709" t="s">
-        <v>2731</v>
+        <v>2730</v>
       </c>
       <c r="C2709" t="s">
-        <v>2719</v>
+        <v>2718</v>
       </c>
     </row>
     <row r="2710" spans="1:3" x14ac:dyDescent="0.3">
@@ -39148,10 +39148,10 @@
         <v>2709</v>
       </c>
       <c r="B2710" t="s">
-        <v>2732</v>
+        <v>2731</v>
       </c>
       <c r="C2710" t="s">
-        <v>2719</v>
+        <v>2718</v>
       </c>
     </row>
     <row r="2711" spans="1:3" x14ac:dyDescent="0.3">
@@ -39159,10 +39159,10 @@
         <v>2710</v>
       </c>
       <c r="B2711" t="s">
-        <v>2733</v>
+        <v>2732</v>
       </c>
       <c r="C2711" t="s">
-        <v>2719</v>
+        <v>2718</v>
       </c>
     </row>
     <row r="2712" spans="1:3" x14ac:dyDescent="0.3">
@@ -39170,10 +39170,10 @@
         <v>2711</v>
       </c>
       <c r="B2712" t="s">
+        <v>2733</v>
+      </c>
+      <c r="C2712" t="s">
         <v>2734</v>
-      </c>
-      <c r="C2712" t="s">
-        <v>2735</v>
       </c>
     </row>
     <row r="2713" spans="1:3" x14ac:dyDescent="0.3">
@@ -39181,10 +39181,10 @@
         <v>2712</v>
       </c>
       <c r="B2713" t="s">
-        <v>2736</v>
+        <v>2735</v>
       </c>
       <c r="C2713" t="s">
-        <v>2735</v>
+        <v>2734</v>
       </c>
     </row>
     <row r="2714" spans="1:3" x14ac:dyDescent="0.3">
@@ -39192,10 +39192,10 @@
         <v>2713</v>
       </c>
       <c r="B2714" t="s">
-        <v>2737</v>
+        <v>2736</v>
       </c>
       <c r="C2714" t="s">
-        <v>2735</v>
+        <v>2734</v>
       </c>
     </row>
     <row r="2715" spans="1:3" x14ac:dyDescent="0.3">
@@ -39203,10 +39203,10 @@
         <v>2714</v>
       </c>
       <c r="B2715" t="s">
+        <v>2737</v>
+      </c>
+      <c r="C2715" t="s">
         <v>2738</v>
-      </c>
-      <c r="C2715" t="s">
-        <v>2739</v>
       </c>
     </row>
     <row r="2716" spans="1:3" x14ac:dyDescent="0.3">
@@ -39214,10 +39214,10 @@
         <v>2715</v>
       </c>
       <c r="B2716" t="s">
-        <v>2740</v>
+        <v>2739</v>
       </c>
       <c r="C2716" t="s">
-        <v>2739</v>
+        <v>2738</v>
       </c>
     </row>
     <row r="2717" spans="1:3" x14ac:dyDescent="0.3">
@@ -39225,10 +39225,10 @@
         <v>2716</v>
       </c>
       <c r="B2717" t="s">
-        <v>2741</v>
+        <v>2740</v>
       </c>
       <c r="C2717" t="s">
-        <v>2739</v>
+        <v>2738</v>
       </c>
     </row>
     <row r="2718" spans="1:3" x14ac:dyDescent="0.3">
@@ -39236,10 +39236,10 @@
         <v>2717</v>
       </c>
       <c r="B2718" t="s">
-        <v>2742</v>
+        <v>2741</v>
       </c>
       <c r="C2718" t="s">
-        <v>2739</v>
+        <v>2738</v>
       </c>
     </row>
     <row r="2719" spans="1:3" x14ac:dyDescent="0.3">
@@ -39247,10 +39247,10 @@
         <v>2718</v>
       </c>
       <c r="B2719" t="s">
+        <v>2742</v>
+      </c>
+      <c r="C2719" t="s">
         <v>2743</v>
-      </c>
-      <c r="C2719" t="s">
-        <v>2744</v>
       </c>
     </row>
     <row r="2720" spans="1:3" x14ac:dyDescent="0.3">
@@ -39258,10 +39258,10 @@
         <v>2719</v>
       </c>
       <c r="B2720" t="s">
-        <v>2745</v>
+        <v>2744</v>
       </c>
       <c r="C2720" t="s">
-        <v>2744</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="2721" spans="1:3" x14ac:dyDescent="0.3">
@@ -39269,10 +39269,10 @@
         <v>2720</v>
       </c>
       <c r="B2721" t="s">
-        <v>2746</v>
+        <v>2745</v>
       </c>
       <c r="C2721" t="s">
-        <v>2744</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="2722" spans="1:3" x14ac:dyDescent="0.3">
@@ -39280,10 +39280,10 @@
         <v>2721</v>
       </c>
       <c r="B2722" t="s">
-        <v>2747</v>
+        <v>2746</v>
       </c>
       <c r="C2722" t="s">
-        <v>2744</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="2723" spans="1:3" x14ac:dyDescent="0.3">
@@ -39291,10 +39291,10 @@
         <v>2722</v>
       </c>
       <c r="B2723" t="s">
-        <v>2748</v>
+        <v>2747</v>
       </c>
       <c r="C2723" t="s">
-        <v>2744</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="2724" spans="1:3" x14ac:dyDescent="0.3">
@@ -39302,10 +39302,10 @@
         <v>2723</v>
       </c>
       <c r="B2724" t="s">
-        <v>2749</v>
+        <v>2748</v>
       </c>
       <c r="C2724" t="s">
-        <v>2744</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="2725" spans="1:3" x14ac:dyDescent="0.3">
@@ -39313,10 +39313,10 @@
         <v>2724</v>
       </c>
       <c r="B2725" t="s">
-        <v>2750</v>
+        <v>2749</v>
       </c>
       <c r="C2725" t="s">
-        <v>2744</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="2726" spans="1:3" x14ac:dyDescent="0.3">
@@ -39324,10 +39324,10 @@
         <v>2725</v>
       </c>
       <c r="B2726" t="s">
-        <v>2751</v>
+        <v>2750</v>
       </c>
       <c r="C2726" t="s">
-        <v>2744</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="2727" spans="1:3" x14ac:dyDescent="0.3">
@@ -39335,10 +39335,10 @@
         <v>2726</v>
       </c>
       <c r="B2727" t="s">
-        <v>2752</v>
+        <v>2751</v>
       </c>
       <c r="C2727" t="s">
-        <v>2744</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="2728" spans="1:3" x14ac:dyDescent="0.3">
@@ -39346,10 +39346,10 @@
         <v>2727</v>
       </c>
       <c r="B2728" t="s">
-        <v>2753</v>
+        <v>2752</v>
       </c>
       <c r="C2728" t="s">
-        <v>2744</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="2729" spans="1:3" x14ac:dyDescent="0.3">
@@ -39357,10 +39357,10 @@
         <v>2728</v>
       </c>
       <c r="B2729" t="s">
-        <v>2754</v>
+        <v>2753</v>
       </c>
       <c r="C2729" t="s">
-        <v>2744</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="2730" spans="1:3" x14ac:dyDescent="0.3">
@@ -39368,10 +39368,10 @@
         <v>2729</v>
       </c>
       <c r="B2730" t="s">
-        <v>2755</v>
+        <v>2754</v>
       </c>
       <c r="C2730" t="s">
-        <v>2744</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="2731" spans="1:3" x14ac:dyDescent="0.3">
@@ -39379,10 +39379,10 @@
         <v>2730</v>
       </c>
       <c r="B2731" t="s">
-        <v>2756</v>
+        <v>2755</v>
       </c>
       <c r="C2731" t="s">
-        <v>2744</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="2732" spans="1:3" x14ac:dyDescent="0.3">
@@ -39390,10 +39390,10 @@
         <v>2731</v>
       </c>
       <c r="B2732" t="s">
-        <v>2757</v>
+        <v>2756</v>
       </c>
       <c r="C2732" t="s">
-        <v>2744</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="2733" spans="1:3" x14ac:dyDescent="0.3">
@@ -39401,10 +39401,10 @@
         <v>2732</v>
       </c>
       <c r="B2733" t="s">
-        <v>2758</v>
+        <v>2757</v>
       </c>
       <c r="C2733" t="s">
-        <v>2744</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="2734" spans="1:3" x14ac:dyDescent="0.3">
@@ -39412,10 +39412,10 @@
         <v>2733</v>
       </c>
       <c r="B2734" t="s">
-        <v>2759</v>
+        <v>2758</v>
       </c>
       <c r="C2734" t="s">
-        <v>2744</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="2735" spans="1:3" x14ac:dyDescent="0.3">
@@ -39423,10 +39423,10 @@
         <v>2734</v>
       </c>
       <c r="B2735" t="s">
-        <v>2760</v>
+        <v>2759</v>
       </c>
       <c r="C2735" t="s">
-        <v>2744</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="2736" spans="1:3" x14ac:dyDescent="0.3">
@@ -39434,10 +39434,10 @@
         <v>2735</v>
       </c>
       <c r="B2736" t="s">
-        <v>2761</v>
+        <v>2760</v>
       </c>
       <c r="C2736" t="s">
-        <v>2744</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="2737" spans="1:3" x14ac:dyDescent="0.3">
@@ -39445,10 +39445,10 @@
         <v>2736</v>
       </c>
       <c r="B2737" t="s">
-        <v>2762</v>
+        <v>2761</v>
       </c>
       <c r="C2737" t="s">
-        <v>2744</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="2738" spans="1:3" x14ac:dyDescent="0.3">
@@ -39456,10 +39456,10 @@
         <v>2737</v>
       </c>
       <c r="B2738" t="s">
-        <v>2763</v>
+        <v>2762</v>
       </c>
       <c r="C2738" t="s">
-        <v>2744</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="2739" spans="1:3" x14ac:dyDescent="0.3">
@@ -39467,10 +39467,10 @@
         <v>2738</v>
       </c>
       <c r="B2739" t="s">
-        <v>2764</v>
+        <v>2763</v>
       </c>
       <c r="C2739" t="s">
-        <v>2744</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="2740" spans="1:3" x14ac:dyDescent="0.3">
@@ -39478,10 +39478,10 @@
         <v>2739</v>
       </c>
       <c r="B2740" t="s">
-        <v>2765</v>
+        <v>2764</v>
       </c>
       <c r="C2740" t="s">
-        <v>2744</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="2741" spans="1:3" x14ac:dyDescent="0.3">
@@ -39489,10 +39489,10 @@
         <v>2740</v>
       </c>
       <c r="B2741" t="s">
-        <v>2766</v>
+        <v>2765</v>
       </c>
       <c r="C2741" t="s">
-        <v>2744</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="2742" spans="1:3" x14ac:dyDescent="0.3">
@@ -39500,10 +39500,10 @@
         <v>2741</v>
       </c>
       <c r="B2742" t="s">
-        <v>2767</v>
+        <v>2766</v>
       </c>
       <c r="C2742" t="s">
-        <v>2744</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="2743" spans="1:3" x14ac:dyDescent="0.3">
@@ -39511,10 +39511,10 @@
         <v>2742</v>
       </c>
       <c r="B2743" t="s">
-        <v>2768</v>
+        <v>2767</v>
       </c>
       <c r="C2743" t="s">
-        <v>2744</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="2744" spans="1:3" x14ac:dyDescent="0.3">
@@ -39522,10 +39522,10 @@
         <v>2743</v>
       </c>
       <c r="B2744" t="s">
-        <v>2769</v>
+        <v>2768</v>
       </c>
       <c r="C2744" t="s">
-        <v>2744</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="2745" spans="1:3" x14ac:dyDescent="0.3">
@@ -39533,10 +39533,10 @@
         <v>2744</v>
       </c>
       <c r="B2745" t="s">
-        <v>2770</v>
+        <v>2769</v>
       </c>
       <c r="C2745" t="s">
-        <v>2744</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="2746" spans="1:3" x14ac:dyDescent="0.3">
@@ -39544,10 +39544,10 @@
         <v>2745</v>
       </c>
       <c r="B2746" t="s">
-        <v>2771</v>
+        <v>2770</v>
       </c>
       <c r="C2746" t="s">
-        <v>2744</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="2747" spans="1:3" x14ac:dyDescent="0.3">
@@ -39555,10 +39555,10 @@
         <v>2746</v>
       </c>
       <c r="B2747" t="s">
-        <v>2772</v>
+        <v>2771</v>
       </c>
       <c r="C2747" t="s">
-        <v>2744</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="2748" spans="1:3" x14ac:dyDescent="0.3">
@@ -39566,10 +39566,10 @@
         <v>2747</v>
       </c>
       <c r="B2748" t="s">
-        <v>2773</v>
+        <v>2772</v>
       </c>
       <c r="C2748" t="s">
-        <v>2744</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="2749" spans="1:3" x14ac:dyDescent="0.3">
@@ -39577,10 +39577,10 @@
         <v>2748</v>
       </c>
       <c r="B2749" t="s">
-        <v>2774</v>
+        <v>2773</v>
       </c>
       <c r="C2749" t="s">
-        <v>2744</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="2750" spans="1:3" x14ac:dyDescent="0.3">
@@ -39588,10 +39588,10 @@
         <v>2749</v>
       </c>
       <c r="B2750" t="s">
-        <v>2775</v>
+        <v>2774</v>
       </c>
       <c r="C2750" t="s">
-        <v>2744</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="2751" spans="1:3" x14ac:dyDescent="0.3">
@@ -39599,10 +39599,10 @@
         <v>2750</v>
       </c>
       <c r="B2751" t="s">
-        <v>2776</v>
+        <v>2775</v>
       </c>
       <c r="C2751" t="s">
-        <v>2744</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="2752" spans="1:3" x14ac:dyDescent="0.3">
@@ -39610,10 +39610,10 @@
         <v>2751</v>
       </c>
       <c r="B2752" t="s">
-        <v>2777</v>
+        <v>2776</v>
       </c>
       <c r="C2752" t="s">
-        <v>2744</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="2753" spans="1:3" x14ac:dyDescent="0.3">
@@ -39621,10 +39621,10 @@
         <v>2752</v>
       </c>
       <c r="B2753" t="s">
-        <v>2778</v>
+        <v>2777</v>
       </c>
       <c r="C2753" t="s">
-        <v>2744</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="2754" spans="1:3" x14ac:dyDescent="0.3">
@@ -39632,10 +39632,10 @@
         <v>2753</v>
       </c>
       <c r="B2754" t="s">
-        <v>2779</v>
+        <v>2778</v>
       </c>
       <c r="C2754" t="s">
-        <v>2744</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="2755" spans="1:3" x14ac:dyDescent="0.3">
@@ -39643,10 +39643,10 @@
         <v>2754</v>
       </c>
       <c r="B2755" t="s">
-        <v>2780</v>
+        <v>2779</v>
       </c>
       <c r="C2755" t="s">
-        <v>2744</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="2756" spans="1:3" x14ac:dyDescent="0.3">
@@ -39654,10 +39654,10 @@
         <v>2755</v>
       </c>
       <c r="B2756" t="s">
-        <v>2781</v>
+        <v>2780</v>
       </c>
       <c r="C2756" t="s">
-        <v>2744</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="2757" spans="1:3" x14ac:dyDescent="0.3">
@@ -39665,10 +39665,10 @@
         <v>2756</v>
       </c>
       <c r="B2757" t="s">
-        <v>2782</v>
+        <v>2781</v>
       </c>
       <c r="C2757" t="s">
-        <v>2744</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="2758" spans="1:3" x14ac:dyDescent="0.3">
@@ -39676,10 +39676,10 @@
         <v>2757</v>
       </c>
       <c r="B2758" t="s">
-        <v>2783</v>
+        <v>2782</v>
       </c>
       <c r="C2758" t="s">
-        <v>2744</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="2759" spans="1:3" x14ac:dyDescent="0.3">
@@ -39687,10 +39687,10 @@
         <v>2758</v>
       </c>
       <c r="B2759" t="s">
-        <v>2784</v>
+        <v>2783</v>
       </c>
       <c r="C2759" t="s">
-        <v>2744</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="2760" spans="1:3" x14ac:dyDescent="0.3">
@@ -39698,10 +39698,10 @@
         <v>2759</v>
       </c>
       <c r="B2760" t="s">
-        <v>2785</v>
+        <v>2784</v>
       </c>
       <c r="C2760" t="s">
-        <v>2744</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="2761" spans="1:3" x14ac:dyDescent="0.3">
@@ -39709,10 +39709,10 @@
         <v>2760</v>
       </c>
       <c r="B2761" t="s">
-        <v>2786</v>
+        <v>2785</v>
       </c>
       <c r="C2761" t="s">
-        <v>2744</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="2762" spans="1:3" x14ac:dyDescent="0.3">
@@ -39720,10 +39720,10 @@
         <v>2761</v>
       </c>
       <c r="B2762" t="s">
-        <v>2787</v>
+        <v>2786</v>
       </c>
       <c r="C2762" t="s">
-        <v>2744</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="2763" spans="1:3" x14ac:dyDescent="0.3">
@@ -39731,10 +39731,10 @@
         <v>2762</v>
       </c>
       <c r="B2763" t="s">
-        <v>2788</v>
+        <v>2787</v>
       </c>
       <c r="C2763" t="s">
-        <v>2744</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="2764" spans="1:3" x14ac:dyDescent="0.3">
@@ -39742,10 +39742,10 @@
         <v>2763</v>
       </c>
       <c r="B2764" t="s">
-        <v>2789</v>
+        <v>2788</v>
       </c>
       <c r="C2764" t="s">
-        <v>2744</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="2765" spans="1:3" x14ac:dyDescent="0.3">
@@ -39753,10 +39753,10 @@
         <v>2764</v>
       </c>
       <c r="B2765" t="s">
-        <v>2790</v>
+        <v>2789</v>
       </c>
       <c r="C2765" t="s">
-        <v>2744</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="2766" spans="1:3" x14ac:dyDescent="0.3">
@@ -39764,10 +39764,10 @@
         <v>2765</v>
       </c>
       <c r="B2766" t="s">
-        <v>2791</v>
+        <v>2790</v>
       </c>
       <c r="C2766" t="s">
-        <v>2744</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="2767" spans="1:3" x14ac:dyDescent="0.3">
@@ -39775,10 +39775,10 @@
         <v>2766</v>
       </c>
       <c r="B2767" t="s">
-        <v>2792</v>
+        <v>2791</v>
       </c>
       <c r="C2767" t="s">
-        <v>2744</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="2768" spans="1:3" x14ac:dyDescent="0.3">
@@ -39786,10 +39786,10 @@
         <v>2767</v>
       </c>
       <c r="B2768" t="s">
-        <v>2793</v>
+        <v>2792</v>
       </c>
       <c r="C2768" t="s">
-        <v>2744</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="2769" spans="1:3" x14ac:dyDescent="0.3">
@@ -39797,10 +39797,10 @@
         <v>2768</v>
       </c>
       <c r="B2769" t="s">
-        <v>2794</v>
+        <v>2793</v>
       </c>
       <c r="C2769" t="s">
-        <v>2744</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="2770" spans="1:3" x14ac:dyDescent="0.3">
@@ -39808,10 +39808,10 @@
         <v>2769</v>
       </c>
       <c r="B2770" t="s">
-        <v>2795</v>
+        <v>2794</v>
       </c>
       <c r="C2770" t="s">
-        <v>2744</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="2771" spans="1:3" x14ac:dyDescent="0.3">
@@ -39819,10 +39819,10 @@
         <v>2770</v>
       </c>
       <c r="B2771" t="s">
-        <v>2796</v>
+        <v>2795</v>
       </c>
       <c r="C2771" t="s">
-        <v>2744</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="2772" spans="1:3" x14ac:dyDescent="0.3">
@@ -39830,10 +39830,10 @@
         <v>2771</v>
       </c>
       <c r="B2772" t="s">
-        <v>2797</v>
+        <v>2796</v>
       </c>
       <c r="C2772" t="s">
-        <v>2744</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="2773" spans="1:3" x14ac:dyDescent="0.3">
@@ -39841,10 +39841,10 @@
         <v>2772</v>
       </c>
       <c r="B2773" t="s">
-        <v>2798</v>
+        <v>2797</v>
       </c>
       <c r="C2773" t="s">
-        <v>2744</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="2774" spans="1:3" x14ac:dyDescent="0.3">
@@ -39852,10 +39852,10 @@
         <v>2773</v>
       </c>
       <c r="B2774" t="s">
-        <v>2799</v>
+        <v>2798</v>
       </c>
       <c r="C2774" t="s">
-        <v>2744</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="2775" spans="1:3" x14ac:dyDescent="0.3">
@@ -39863,10 +39863,10 @@
         <v>2774</v>
       </c>
       <c r="B2775" t="s">
-        <v>2800</v>
+        <v>2799</v>
       </c>
       <c r="C2775" t="s">
-        <v>2744</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="2776" spans="1:3" x14ac:dyDescent="0.3">
@@ -39874,10 +39874,10 @@
         <v>2775</v>
       </c>
       <c r="B2776" t="s">
-        <v>2801</v>
+        <v>2800</v>
       </c>
       <c r="C2776" t="s">
-        <v>2744</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="2777" spans="1:3" x14ac:dyDescent="0.3">
@@ -39885,10 +39885,10 @@
         <v>2776</v>
       </c>
       <c r="B2777" t="s">
-        <v>2802</v>
+        <v>2801</v>
       </c>
       <c r="C2777" t="s">
-        <v>2744</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="2778" spans="1:3" x14ac:dyDescent="0.3">
@@ -39896,10 +39896,10 @@
         <v>2777</v>
       </c>
       <c r="B2778" t="s">
-        <v>2803</v>
+        <v>2802</v>
       </c>
       <c r="C2778" t="s">
-        <v>2744</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="2779" spans="1:3" x14ac:dyDescent="0.3">
@@ -39907,10 +39907,10 @@
         <v>2778</v>
       </c>
       <c r="B2779" t="s">
-        <v>2804</v>
+        <v>2803</v>
       </c>
       <c r="C2779" t="s">
-        <v>2744</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="2780" spans="1:3" x14ac:dyDescent="0.3">
@@ -39918,10 +39918,10 @@
         <v>2779</v>
       </c>
       <c r="B2780" t="s">
-        <v>2805</v>
+        <v>2804</v>
       </c>
       <c r="C2780" t="s">
-        <v>2744</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="2781" spans="1:3" x14ac:dyDescent="0.3">
@@ -39929,10 +39929,10 @@
         <v>2780</v>
       </c>
       <c r="B2781" t="s">
-        <v>2806</v>
+        <v>2805</v>
       </c>
       <c r="C2781" t="s">
-        <v>2744</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="2782" spans="1:3" x14ac:dyDescent="0.3">
@@ -39940,10 +39940,10 @@
         <v>2781</v>
       </c>
       <c r="B2782" t="s">
-        <v>2807</v>
+        <v>2806</v>
       </c>
       <c r="C2782" t="s">
-        <v>2744</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="2783" spans="1:3" x14ac:dyDescent="0.3">
@@ -39951,10 +39951,10 @@
         <v>2782</v>
       </c>
       <c r="B2783" t="s">
-        <v>2808</v>
+        <v>2807</v>
       </c>
       <c r="C2783" t="s">
-        <v>2744</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="2784" spans="1:3" x14ac:dyDescent="0.3">
@@ -39962,10 +39962,10 @@
         <v>2783</v>
       </c>
       <c r="B2784" t="s">
-        <v>2809</v>
+        <v>2808</v>
       </c>
       <c r="C2784" t="s">
-        <v>2744</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="2785" spans="1:3" x14ac:dyDescent="0.3">
@@ -39973,10 +39973,10 @@
         <v>2784</v>
       </c>
       <c r="B2785" t="s">
-        <v>2810</v>
+        <v>2809</v>
       </c>
       <c r="C2785" t="s">
-        <v>2744</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="2786" spans="1:3" x14ac:dyDescent="0.3">
@@ -39984,10 +39984,10 @@
         <v>2785</v>
       </c>
       <c r="B2786" t="s">
-        <v>2811</v>
+        <v>2810</v>
       </c>
       <c r="C2786" t="s">
-        <v>2744</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="2787" spans="1:3" x14ac:dyDescent="0.3">
@@ -39995,10 +39995,10 @@
         <v>2786</v>
       </c>
       <c r="B2787" t="s">
-        <v>2812</v>
+        <v>2811</v>
       </c>
       <c r="C2787" t="s">
-        <v>2744</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="2788" spans="1:3" x14ac:dyDescent="0.3">
@@ -40006,10 +40006,10 @@
         <v>2787</v>
       </c>
       <c r="B2788" t="s">
-        <v>2813</v>
+        <v>2812</v>
       </c>
       <c r="C2788" t="s">
-        <v>2744</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="2789" spans="1:3" x14ac:dyDescent="0.3">
@@ -40017,10 +40017,10 @@
         <v>2788</v>
       </c>
       <c r="B2789" t="s">
-        <v>2814</v>
+        <v>2813</v>
       </c>
       <c r="C2789" t="s">
-        <v>2744</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="2790" spans="1:3" x14ac:dyDescent="0.3">
@@ -40028,10 +40028,10 @@
         <v>2789</v>
       </c>
       <c r="B2790" t="s">
-        <v>2815</v>
+        <v>2814</v>
       </c>
       <c r="C2790" t="s">
-        <v>2744</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="2791" spans="1:3" x14ac:dyDescent="0.3">
@@ -40039,10 +40039,10 @@
         <v>2790</v>
       </c>
       <c r="B2791" t="s">
-        <v>2816</v>
+        <v>2815</v>
       </c>
       <c r="C2791" t="s">
-        <v>2744</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="2792" spans="1:3" x14ac:dyDescent="0.3">
@@ -40050,10 +40050,10 @@
         <v>2791</v>
       </c>
       <c r="B2792" t="s">
-        <v>2817</v>
+        <v>2816</v>
       </c>
       <c r="C2792" t="s">
-        <v>2744</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="2793" spans="1:3" x14ac:dyDescent="0.3">
@@ -40061,10 +40061,10 @@
         <v>2792</v>
       </c>
       <c r="B2793" t="s">
-        <v>2818</v>
+        <v>2817</v>
       </c>
       <c r="C2793" t="s">
-        <v>2744</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="2794" spans="1:3" x14ac:dyDescent="0.3">
@@ -40072,10 +40072,10 @@
         <v>2793</v>
       </c>
       <c r="B2794" t="s">
-        <v>2819</v>
+        <v>2818</v>
       </c>
       <c r="C2794" t="s">
-        <v>2744</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="2795" spans="1:3" x14ac:dyDescent="0.3">
@@ -40083,10 +40083,10 @@
         <v>2794</v>
       </c>
       <c r="B2795" t="s">
-        <v>2820</v>
+        <v>2819</v>
       </c>
       <c r="C2795" t="s">
-        <v>2744</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="2796" spans="1:3" x14ac:dyDescent="0.3">
@@ -40094,10 +40094,10 @@
         <v>2795</v>
       </c>
       <c r="B2796" t="s">
-        <v>2821</v>
+        <v>2820</v>
       </c>
       <c r="C2796" t="s">
-        <v>2744</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="2797" spans="1:3" x14ac:dyDescent="0.3">
@@ -40105,10 +40105,10 @@
         <v>2796</v>
       </c>
       <c r="B2797" t="s">
-        <v>2822</v>
+        <v>2821</v>
       </c>
       <c r="C2797" t="s">
-        <v>2744</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="2798" spans="1:3" x14ac:dyDescent="0.3">
@@ -40116,10 +40116,10 @@
         <v>2797</v>
       </c>
       <c r="B2798" t="s">
-        <v>2823</v>
+        <v>2822</v>
       </c>
       <c r="C2798" t="s">
-        <v>2744</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="2799" spans="1:3" x14ac:dyDescent="0.3">
@@ -40127,10 +40127,10 @@
         <v>2798</v>
       </c>
       <c r="B2799" t="s">
-        <v>2824</v>
+        <v>2823</v>
       </c>
       <c r="C2799" t="s">
-        <v>2744</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="2800" spans="1:3" x14ac:dyDescent="0.3">
@@ -40138,10 +40138,10 @@
         <v>2799</v>
       </c>
       <c r="B2800" t="s">
-        <v>2825</v>
+        <v>2824</v>
       </c>
       <c r="C2800" t="s">
-        <v>2744</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="2801" spans="1:3" x14ac:dyDescent="0.3">
@@ -40149,10 +40149,10 @@
         <v>2800</v>
       </c>
       <c r="B2801" t="s">
-        <v>2826</v>
+        <v>2825</v>
       </c>
       <c r="C2801" t="s">
-        <v>2744</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="2802" spans="1:3" x14ac:dyDescent="0.3">
@@ -40160,10 +40160,10 @@
         <v>2801</v>
       </c>
       <c r="B2802" t="s">
-        <v>2827</v>
+        <v>2826</v>
       </c>
       <c r="C2802" t="s">
-        <v>2744</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="2803" spans="1:3" x14ac:dyDescent="0.3">
@@ -40171,10 +40171,10 @@
         <v>2802</v>
       </c>
       <c r="B2803" t="s">
-        <v>2828</v>
+        <v>2827</v>
       </c>
       <c r="C2803" t="s">
-        <v>2744</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="2804" spans="1:3" x14ac:dyDescent="0.3">
@@ -40182,10 +40182,10 @@
         <v>2803</v>
       </c>
       <c r="B2804" t="s">
-        <v>2829</v>
+        <v>2828</v>
       </c>
       <c r="C2804" t="s">
-        <v>2744</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="2805" spans="1:3" x14ac:dyDescent="0.3">
@@ -40193,10 +40193,10 @@
         <v>2804</v>
       </c>
       <c r="B2805" t="s">
-        <v>2830</v>
+        <v>2829</v>
       </c>
       <c r="C2805" t="s">
-        <v>2744</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="2806" spans="1:3" x14ac:dyDescent="0.3">
@@ -40204,10 +40204,10 @@
         <v>2805</v>
       </c>
       <c r="B2806" t="s">
-        <v>2831</v>
+        <v>2830</v>
       </c>
       <c r="C2806" t="s">
-        <v>2744</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="2807" spans="1:3" x14ac:dyDescent="0.3">
@@ -40215,10 +40215,10 @@
         <v>2806</v>
       </c>
       <c r="B2807" t="s">
-        <v>2832</v>
+        <v>2831</v>
       </c>
       <c r="C2807" t="s">
-        <v>2744</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="2808" spans="1:3" x14ac:dyDescent="0.3">
@@ -40226,10 +40226,10 @@
         <v>2807</v>
       </c>
       <c r="B2808" t="s">
-        <v>2833</v>
+        <v>2832</v>
       </c>
       <c r="C2808" t="s">
-        <v>2744</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="2809" spans="1:3" x14ac:dyDescent="0.3">
@@ -40237,10 +40237,10 @@
         <v>2808</v>
       </c>
       <c r="B2809" t="s">
-        <v>2834</v>
+        <v>2833</v>
       </c>
       <c r="C2809" t="s">
-        <v>2744</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="2810" spans="1:3" x14ac:dyDescent="0.3">
@@ -40248,10 +40248,10 @@
         <v>2809</v>
       </c>
       <c r="B2810" t="s">
-        <v>2835</v>
+        <v>2834</v>
       </c>
       <c r="C2810" t="s">
-        <v>2744</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="2811" spans="1:3" x14ac:dyDescent="0.3">
@@ -40259,10 +40259,10 @@
         <v>2810</v>
       </c>
       <c r="B2811" t="s">
-        <v>2836</v>
+        <v>2835</v>
       </c>
       <c r="C2811" t="s">
-        <v>2744</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="2812" spans="1:3" x14ac:dyDescent="0.3">
@@ -40270,10 +40270,10 @@
         <v>2811</v>
       </c>
       <c r="B2812" t="s">
-        <v>2837</v>
+        <v>2836</v>
       </c>
       <c r="C2812" t="s">
-        <v>2744</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="2813" spans="1:3" x14ac:dyDescent="0.3">
@@ -40281,10 +40281,10 @@
         <v>2812</v>
       </c>
       <c r="B2813" t="s">
-        <v>2838</v>
+        <v>2837</v>
       </c>
       <c r="C2813" t="s">
-        <v>2744</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="2814" spans="1:3" x14ac:dyDescent="0.3">
@@ -40292,10 +40292,10 @@
         <v>2813</v>
       </c>
       <c r="B2814" t="s">
-        <v>2839</v>
+        <v>2838</v>
       </c>
       <c r="C2814" t="s">
-        <v>2744</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="2815" spans="1:3" x14ac:dyDescent="0.3">
@@ -40303,10 +40303,10 @@
         <v>2814</v>
       </c>
       <c r="B2815" t="s">
-        <v>2840</v>
+        <v>2839</v>
       </c>
       <c r="C2815" t="s">
-        <v>2744</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="2816" spans="1:3" x14ac:dyDescent="0.3">
@@ -40314,10 +40314,10 @@
         <v>2815</v>
       </c>
       <c r="B2816" t="s">
-        <v>2841</v>
+        <v>2840</v>
       </c>
       <c r="C2816" t="s">
-        <v>2744</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="2817" spans="1:3" x14ac:dyDescent="0.3">
@@ -40325,10 +40325,10 @@
         <v>2816</v>
       </c>
       <c r="B2817" t="s">
-        <v>2842</v>
+        <v>2841</v>
       </c>
       <c r="C2817" t="s">
-        <v>2744</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="2818" spans="1:3" x14ac:dyDescent="0.3">
@@ -40336,10 +40336,10 @@
         <v>2817</v>
       </c>
       <c r="B2818" t="s">
-        <v>2843</v>
+        <v>2842</v>
       </c>
       <c r="C2818" t="s">
-        <v>2744</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="2819" spans="1:3" x14ac:dyDescent="0.3">
@@ -40347,10 +40347,10 @@
         <v>2818</v>
       </c>
       <c r="B2819" t="s">
-        <v>2844</v>
+        <v>2843</v>
       </c>
       <c r="C2819" t="s">
-        <v>2744</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="2820" spans="1:3" x14ac:dyDescent="0.3">
@@ -40358,10 +40358,10 @@
         <v>2819</v>
       </c>
       <c r="B2820" t="s">
-        <v>2845</v>
+        <v>2844</v>
       </c>
       <c r="C2820" t="s">
-        <v>2744</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="2821" spans="1:3" x14ac:dyDescent="0.3">
@@ -40369,10 +40369,10 @@
         <v>2820</v>
       </c>
       <c r="B2821" t="s">
-        <v>2846</v>
+        <v>2845</v>
       </c>
       <c r="C2821" t="s">
-        <v>2744</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="2822" spans="1:3" x14ac:dyDescent="0.3">
@@ -40380,10 +40380,10 @@
         <v>2821</v>
       </c>
       <c r="B2822" t="s">
-        <v>2847</v>
+        <v>2846</v>
       </c>
       <c r="C2822" t="s">
-        <v>2744</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="2823" spans="1:3" x14ac:dyDescent="0.3">
@@ -40391,10 +40391,10 @@
         <v>2822</v>
       </c>
       <c r="B2823" t="s">
-        <v>2848</v>
+        <v>2847</v>
       </c>
       <c r="C2823" t="s">
-        <v>2744</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="2824" spans="1:3" x14ac:dyDescent="0.3">
@@ -40402,10 +40402,10 @@
         <v>2823</v>
       </c>
       <c r="B2824" t="s">
-        <v>2849</v>
+        <v>2848</v>
       </c>
       <c r="C2824" t="s">
-        <v>2744</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="2825" spans="1:3" x14ac:dyDescent="0.3">
@@ -40413,10 +40413,10 @@
         <v>2824</v>
       </c>
       <c r="B2825" t="s">
-        <v>2850</v>
+        <v>2849</v>
       </c>
       <c r="C2825" t="s">
-        <v>2744</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="2826" spans="1:3" x14ac:dyDescent="0.3">
@@ -40424,10 +40424,10 @@
         <v>2825</v>
       </c>
       <c r="B2826" t="s">
-        <v>2851</v>
+        <v>2850</v>
       </c>
       <c r="C2826" t="s">
-        <v>2744</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="2827" spans="1:3" x14ac:dyDescent="0.3">
@@ -40435,10 +40435,10 @@
         <v>2826</v>
       </c>
       <c r="B2827" t="s">
-        <v>2852</v>
+        <v>2851</v>
       </c>
       <c r="C2827" t="s">
-        <v>2744</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="2828" spans="1:3" x14ac:dyDescent="0.3">
@@ -40446,10 +40446,10 @@
         <v>2827</v>
       </c>
       <c r="B2828" t="s">
-        <v>2853</v>
+        <v>2852</v>
       </c>
       <c r="C2828" t="s">
-        <v>2744</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="2829" spans="1:3" x14ac:dyDescent="0.3">
@@ -40457,10 +40457,10 @@
         <v>2828</v>
       </c>
       <c r="B2829" t="s">
-        <v>2854</v>
+        <v>2853</v>
       </c>
       <c r="C2829" t="s">
-        <v>2744</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="2830" spans="1:3" x14ac:dyDescent="0.3">
@@ -40468,10 +40468,10 @@
         <v>2829</v>
       </c>
       <c r="B2830" t="s">
+        <v>2854</v>
+      </c>
+      <c r="C2830" t="s">
         <v>2855</v>
-      </c>
-      <c r="C2830" t="s">
-        <v>2856</v>
       </c>
     </row>
     <row r="2831" spans="1:3" x14ac:dyDescent="0.3">
@@ -40479,10 +40479,10 @@
         <v>2830</v>
       </c>
       <c r="B2831" t="s">
+        <v>2856</v>
+      </c>
+      <c r="C2831" t="s">
         <v>2857</v>
-      </c>
-      <c r="C2831" t="s">
-        <v>2858</v>
       </c>
     </row>
     <row r="2832" spans="1:3" x14ac:dyDescent="0.3">
@@ -40490,10 +40490,10 @@
         <v>2831</v>
       </c>
       <c r="B2832" t="s">
+        <v>2858</v>
+      </c>
+      <c r="C2832" t="s">
         <v>2859</v>
-      </c>
-      <c r="C2832" t="s">
-        <v>2860</v>
       </c>
     </row>
     <row r="2833" spans="1:3" x14ac:dyDescent="0.3">
@@ -40501,10 +40501,10 @@
         <v>2832</v>
       </c>
       <c r="B2833" t="s">
+        <v>2860</v>
+      </c>
+      <c r="C2833" t="s">
         <v>2861</v>
-      </c>
-      <c r="C2833" t="s">
-        <v>2862</v>
       </c>
     </row>
     <row r="2834" spans="1:3" x14ac:dyDescent="0.3">
@@ -40512,10 +40512,10 @@
         <v>2833</v>
       </c>
       <c r="B2834" t="s">
-        <v>2863</v>
+        <v>2862</v>
       </c>
       <c r="C2834" t="s">
-        <v>2862</v>
+        <v>2861</v>
       </c>
     </row>
     <row r="2835" spans="1:3" x14ac:dyDescent="0.3">
@@ -40523,10 +40523,10 @@
         <v>2834</v>
       </c>
       <c r="B2835" t="s">
-        <v>2864</v>
+        <v>2863</v>
       </c>
       <c r="C2835" t="s">
-        <v>2862</v>
+        <v>2861</v>
       </c>
     </row>
     <row r="2836" spans="1:3" x14ac:dyDescent="0.3">
@@ -40534,10 +40534,10 @@
         <v>2835</v>
       </c>
       <c r="B2836" t="s">
-        <v>2865</v>
+        <v>2864</v>
       </c>
       <c r="C2836" t="s">
-        <v>2862</v>
+        <v>2861</v>
       </c>
     </row>
     <row r="2837" spans="1:3" x14ac:dyDescent="0.3">
@@ -40545,10 +40545,10 @@
         <v>2836</v>
       </c>
       <c r="B2837" t="s">
-        <v>2866</v>
+        <v>2865</v>
       </c>
       <c r="C2837" t="s">
-        <v>2862</v>
+        <v>2861</v>
       </c>
     </row>
     <row r="2838" spans="1:3" x14ac:dyDescent="0.3">
@@ -40556,10 +40556,10 @@
         <v>2837</v>
       </c>
       <c r="B2838" t="s">
-        <v>2867</v>
+        <v>2866</v>
       </c>
       <c r="C2838" t="s">
-        <v>2862</v>
+        <v>2861</v>
       </c>
     </row>
     <row r="2839" spans="1:3" x14ac:dyDescent="0.3">
@@ -40567,10 +40567,10 @@
         <v>2838</v>
       </c>
       <c r="B2839" t="s">
-        <v>2868</v>
+        <v>2867</v>
       </c>
       <c r="C2839" t="s">
-        <v>2862</v>
+        <v>2861</v>
       </c>
     </row>
     <row r="2840" spans="1:3" x14ac:dyDescent="0.3">
@@ -40578,10 +40578,10 @@
         <v>2839</v>
       </c>
       <c r="B2840" t="s">
-        <v>2869</v>
+        <v>2868</v>
       </c>
       <c r="C2840" t="s">
-        <v>2862</v>
+        <v>2861</v>
       </c>
     </row>
     <row r="2841" spans="1:3" x14ac:dyDescent="0.3">
@@ -40589,10 +40589,10 @@
         <v>2840</v>
       </c>
       <c r="B2841" t="s">
-        <v>2870</v>
+        <v>2869</v>
       </c>
       <c r="C2841" t="s">
-        <v>2862</v>
+        <v>2861</v>
       </c>
     </row>
     <row r="2842" spans="1:3" x14ac:dyDescent="0.3">
@@ -40600,10 +40600,10 @@
         <v>2841</v>
       </c>
       <c r="B2842" t="s">
-        <v>2871</v>
+        <v>2870</v>
       </c>
       <c r="C2842" t="s">
-        <v>2862</v>
+        <v>2861</v>
       </c>
     </row>
     <row r="2843" spans="1:3" x14ac:dyDescent="0.3">
@@ -40611,10 +40611,10 @@
         <v>2842</v>
       </c>
       <c r="B2843" t="s">
-        <v>2872</v>
+        <v>2871</v>
       </c>
       <c r="C2843" t="s">
-        <v>2862</v>
+        <v>2861</v>
       </c>
     </row>
     <row r="2844" spans="1:3" x14ac:dyDescent="0.3">
@@ -40622,10 +40622,10 @@
         <v>2843</v>
       </c>
       <c r="B2844" t="s">
-        <v>2873</v>
+        <v>2872</v>
       </c>
       <c r="C2844" t="s">
-        <v>2862</v>
+        <v>2861</v>
       </c>
     </row>
     <row r="2845" spans="1:3" x14ac:dyDescent="0.3">
@@ -40633,10 +40633,10 @@
         <v>2844</v>
       </c>
       <c r="B2845" t="s">
-        <v>2874</v>
+        <v>2873</v>
       </c>
       <c r="C2845" t="s">
-        <v>2862</v>
+        <v>2861</v>
       </c>
     </row>
     <row r="2846" spans="1:3" x14ac:dyDescent="0.3">
@@ -40644,10 +40644,10 @@
         <v>2845</v>
       </c>
       <c r="B2846" t="s">
-        <v>2875</v>
+        <v>2874</v>
       </c>
       <c r="C2846" t="s">
-        <v>2862</v>
+        <v>2861</v>
       </c>
     </row>
     <row r="2847" spans="1:3" x14ac:dyDescent="0.3">
@@ -40655,10 +40655,10 @@
         <v>2846</v>
       </c>
       <c r="B2847" t="s">
-        <v>2876</v>
+        <v>2875</v>
       </c>
       <c r="C2847" t="s">
-        <v>2862</v>
+        <v>2861</v>
       </c>
     </row>
     <row r="2848" spans="1:3" x14ac:dyDescent="0.3">
@@ -40666,10 +40666,10 @@
         <v>2847</v>
       </c>
       <c r="B2848" t="s">
-        <v>2877</v>
+        <v>2876</v>
       </c>
       <c r="C2848" t="s">
-        <v>2862</v>
+        <v>2861</v>
       </c>
     </row>
     <row r="2849" spans="1:3" x14ac:dyDescent="0.3">
@@ -40677,10 +40677,10 @@
         <v>2848</v>
       </c>
       <c r="B2849" t="s">
-        <v>2878</v>
+        <v>2877</v>
       </c>
       <c r="C2849" t="s">
-        <v>2862</v>
+        <v>2861</v>
       </c>
     </row>
     <row r="2850" spans="1:3" x14ac:dyDescent="0.3">
@@ -40688,10 +40688,10 @@
         <v>2849</v>
       </c>
       <c r="B2850" t="s">
-        <v>2879</v>
+        <v>2878</v>
       </c>
       <c r="C2850" t="s">
-        <v>2862</v>
+        <v>2861</v>
       </c>
     </row>
     <row r="2851" spans="1:3" x14ac:dyDescent="0.3">
@@ -40699,10 +40699,10 @@
         <v>2850</v>
       </c>
       <c r="B2851" t="s">
-        <v>2880</v>
+        <v>2879</v>
       </c>
       <c r="C2851" t="s">
-        <v>2862</v>
+        <v>2861</v>
       </c>
     </row>
     <row r="2852" spans="1:3" x14ac:dyDescent="0.3">
@@ -40710,10 +40710,10 @@
         <v>2851</v>
       </c>
       <c r="B2852" t="s">
-        <v>2881</v>
+        <v>2880</v>
       </c>
       <c r="C2852" t="s">
-        <v>2862</v>
+        <v>2861</v>
       </c>
     </row>
     <row r="2853" spans="1:3" x14ac:dyDescent="0.3">
@@ -40721,10 +40721,10 @@
         <v>2852</v>
       </c>
       <c r="B2853" t="s">
-        <v>2882</v>
+        <v>2881</v>
       </c>
       <c r="C2853" t="s">
-        <v>2862</v>
+        <v>2861</v>
       </c>
     </row>
     <row r="2854" spans="1:3" x14ac:dyDescent="0.3">
@@ -40732,10 +40732,10 @@
         <v>2853</v>
       </c>
       <c r="B2854" t="s">
-        <v>2883</v>
+        <v>2882</v>
       </c>
       <c r="C2854" t="s">
-        <v>2862</v>
+        <v>2861</v>
       </c>
     </row>
     <row r="2855" spans="1:3" x14ac:dyDescent="0.3">
@@ -40743,10 +40743,10 @@
         <v>2854</v>
       </c>
       <c r="B2855" t="s">
-        <v>2884</v>
+        <v>2883</v>
       </c>
       <c r="C2855" t="s">
-        <v>2862</v>
+        <v>2861</v>
       </c>
     </row>
     <row r="2856" spans="1:3" x14ac:dyDescent="0.3">
@@ -40754,10 +40754,10 @@
         <v>2855</v>
       </c>
       <c r="B2856" t="s">
-        <v>2885</v>
+        <v>2884</v>
       </c>
       <c r="C2856" t="s">
-        <v>2862</v>
+        <v>2861</v>
       </c>
     </row>
     <row r="2857" spans="1:3" x14ac:dyDescent="0.3">
@@ -40765,10 +40765,10 @@
         <v>2856</v>
       </c>
       <c r="B2857" t="s">
-        <v>2886</v>
+        <v>2885</v>
       </c>
       <c r="C2857" t="s">
-        <v>2862</v>
+        <v>2861</v>
       </c>
     </row>
     <row r="2858" spans="1:3" x14ac:dyDescent="0.3">
@@ -40776,10 +40776,10 @@
         <v>2857</v>
       </c>
       <c r="B2858" t="s">
-        <v>2887</v>
+        <v>2886</v>
       </c>
       <c r="C2858" t="s">
-        <v>2862</v>
+        <v>2861</v>
       </c>
     </row>
     <row r="2859" spans="1:3" x14ac:dyDescent="0.3">
@@ -40787,10 +40787,10 @@
         <v>2858</v>
       </c>
       <c r="B2859" t="s">
-        <v>2888</v>
+        <v>2887</v>
       </c>
       <c r="C2859" t="s">
-        <v>2862</v>
+        <v>2861</v>
       </c>
     </row>
     <row r="2860" spans="1:3" x14ac:dyDescent="0.3">
@@ -40798,10 +40798,10 @@
         <v>2859</v>
       </c>
       <c r="B2860" t="s">
-        <v>2889</v>
+        <v>2888</v>
       </c>
       <c r="C2860" t="s">
-        <v>2862</v>
+        <v>2861</v>
       </c>
     </row>
     <row r="2861" spans="1:3" x14ac:dyDescent="0.3">
@@ -40809,7 +40809,7 @@
         <v>2860</v>
       </c>
       <c r="B2861" t="s">
-        <v>2890</v>
+        <v>2889</v>
       </c>
       <c r="C2861" t="s">
         <v>293</v>
@@ -40820,7 +40820,7 @@
         <v>2861</v>
       </c>
       <c r="B2862" t="s">
-        <v>2891</v>
+        <v>2890</v>
       </c>
       <c r="C2862" t="s">
         <v>2188</v>
@@ -40831,7 +40831,7 @@
         <v>2862</v>
       </c>
       <c r="B2863" t="s">
-        <v>2892</v>
+        <v>2891</v>
       </c>
       <c r="C2863" t="s">
         <v>2188</v>
@@ -40842,7 +40842,7 @@
         <v>2863</v>
       </c>
       <c r="B2864" t="s">
-        <v>2915</v>
+        <v>2914</v>
       </c>
       <c r="C2864" t="s">
         <v>293</v>
@@ -40853,7 +40853,7 @@
         <v>2864</v>
       </c>
       <c r="B2865" t="s">
-        <v>2916</v>
+        <v>2915</v>
       </c>
       <c r="C2865" t="s">
         <v>293</v>
@@ -40864,7 +40864,7 @@
         <v>2865</v>
       </c>
       <c r="B2866" t="s">
-        <v>2917</v>
+        <v>2916</v>
       </c>
       <c r="C2866" t="s">
         <v>293</v>
@@ -40875,7 +40875,7 @@
         <v>2866</v>
       </c>
       <c r="B2867" t="s">
-        <v>2918</v>
+        <v>2917</v>
       </c>
       <c r="C2867" t="s">
         <v>293</v>
@@ -40886,7 +40886,7 @@
         <v>2867</v>
       </c>
       <c r="B2868" t="s">
-        <v>2893</v>
+        <v>2892</v>
       </c>
       <c r="C2868" t="s">
         <v>293</v>
@@ -40897,7 +40897,7 @@
         <v>2868</v>
       </c>
       <c r="B2869" t="s">
-        <v>2894</v>
+        <v>2893</v>
       </c>
       <c r="C2869" t="s">
         <v>293</v>
@@ -40908,7 +40908,7 @@
         <v>2869</v>
       </c>
       <c r="B2870" t="s">
-        <v>2895</v>
+        <v>2894</v>
       </c>
       <c r="C2870" t="s">
         <v>293</v>
@@ -40919,7 +40919,7 @@
         <v>2870</v>
       </c>
       <c r="B2871" t="s">
-        <v>2896</v>
+        <v>2895</v>
       </c>
       <c r="C2871" t="s">
         <v>293</v>
@@ -40930,7 +40930,7 @@
         <v>2871</v>
       </c>
       <c r="B2872" t="s">
-        <v>2897</v>
+        <v>2896</v>
       </c>
       <c r="C2872" t="s">
         <v>293</v>
@@ -40941,7 +40941,7 @@
         <v>2872</v>
       </c>
       <c r="B2873" t="s">
-        <v>2898</v>
+        <v>2897</v>
       </c>
       <c r="C2873" t="s">
         <v>293</v>
@@ -40952,7 +40952,7 @@
         <v>2873</v>
       </c>
       <c r="B2874" t="s">
-        <v>2899</v>
+        <v>2898</v>
       </c>
       <c r="C2874" t="s">
         <v>293</v>
@@ -40963,7 +40963,7 @@
         <v>2874</v>
       </c>
       <c r="B2875" t="s">
-        <v>2900</v>
+        <v>2899</v>
       </c>
       <c r="C2875" t="s">
         <v>2188</v>
@@ -40974,7 +40974,7 @@
         <v>2875</v>
       </c>
       <c r="B2876" t="s">
-        <v>2901</v>
+        <v>2900</v>
       </c>
       <c r="C2876" t="s">
         <v>2188</v>
@@ -40985,7 +40985,7 @@
         <v>2876</v>
       </c>
       <c r="B2877" t="s">
-        <v>2902</v>
+        <v>2901</v>
       </c>
       <c r="C2877" t="s">
         <v>2188</v>
@@ -40996,7 +40996,7 @@
         <v>2877</v>
       </c>
       <c r="B2878" t="s">
-        <v>2903</v>
+        <v>2902</v>
       </c>
       <c r="C2878" t="s">
         <v>2188</v>
@@ -41007,7 +41007,7 @@
         <v>2878</v>
       </c>
       <c r="B2879" t="s">
-        <v>2919</v>
+        <v>2918</v>
       </c>
       <c r="C2879" t="s">
         <v>4</v>
@@ -41018,10 +41018,10 @@
         <v>2879</v>
       </c>
       <c r="B2880" t="s">
+        <v>2903</v>
+      </c>
+      <c r="C2880" t="s">
         <v>2904</v>
-      </c>
-      <c r="C2880" t="s">
-        <v>2905</v>
       </c>
     </row>
     <row r="2881" spans="1:3" x14ac:dyDescent="0.3">
@@ -41029,7 +41029,7 @@
         <v>2880</v>
       </c>
       <c r="B2881" t="s">
-        <v>2911</v>
+        <v>2910</v>
       </c>
       <c r="C2881" t="s">
         <v>2188</v>
@@ -41040,10 +41040,10 @@
         <v>2881</v>
       </c>
       <c r="B2882" t="s">
-        <v>2912</v>
+        <v>2911</v>
       </c>
       <c r="C2882" t="s">
-        <v>2605</v>
+        <v>2604</v>
       </c>
     </row>
     <row r="2883" spans="1:3" x14ac:dyDescent="0.3">
@@ -41051,7 +41051,7 @@
         <v>2882</v>
       </c>
       <c r="B2883" t="s">
-        <v>2913</v>
+        <v>2912</v>
       </c>
       <c r="C2883" t="s">
         <v>2188</v>
@@ -41062,7 +41062,7 @@
         <v>2883</v>
       </c>
       <c r="B2884" t="s">
-        <v>2914</v>
+        <v>2913</v>
       </c>
       <c r="C2884" t="s">
         <v>2188</v>
@@ -41073,7 +41073,7 @@
         <v>2884</v>
       </c>
       <c r="B2885" t="s">
-        <v>2908</v>
+        <v>2907</v>
       </c>
       <c r="C2885" t="s">
         <v>2188</v>
@@ -41084,7 +41084,7 @@
         <v>2885</v>
       </c>
       <c r="B2886" t="s">
-        <v>2909</v>
+        <v>2908</v>
       </c>
       <c r="C2886" t="s">
         <v>2188</v>
@@ -41095,7 +41095,7 @@
         <v>2886</v>
       </c>
       <c r="B2887" t="s">
-        <v>2910</v>
+        <v>2909</v>
       </c>
       <c r="C2887" t="s">
         <v>97</v>
@@ -41106,7 +41106,7 @@
         <v>2887</v>
       </c>
       <c r="B2888" t="s">
-        <v>2920</v>
+        <v>2919</v>
       </c>
       <c r="C2888" t="s">
         <v>2188</v>
@@ -41117,10 +41117,10 @@
         <v>2888</v>
       </c>
       <c r="B2889" t="s">
-        <v>2715</v>
+        <v>2714</v>
       </c>
       <c r="C2889" t="s">
-        <v>2695</v>
+        <v>2694</v>
       </c>
     </row>
     <row r="2890" spans="1:3" x14ac:dyDescent="0.3">
@@ -41128,10 +41128,10 @@
         <v>2889</v>
       </c>
       <c r="B2890" t="s">
-        <v>2716</v>
+        <v>2715</v>
       </c>
       <c r="C2890" t="s">
-        <v>2695</v>
+        <v>2694</v>
       </c>
     </row>
     <row r="2891" spans="1:3" x14ac:dyDescent="0.3">
@@ -41139,10 +41139,10 @@
         <v>2890</v>
       </c>
       <c r="B2891" t="s">
-        <v>2921</v>
+        <v>2920</v>
       </c>
       <c r="C2891" t="s">
-        <v>2695</v>
+        <v>2694</v>
       </c>
     </row>
     <row r="2892" spans="1:3" x14ac:dyDescent="0.3">
@@ -41150,10 +41150,10 @@
         <v>2891</v>
       </c>
       <c r="B2892" t="s">
+        <v>2921</v>
+      </c>
+      <c r="C2892" t="s">
         <v>2922</v>
-      </c>
-      <c r="C2892" t="s">
-        <v>2923</v>
       </c>
     </row>
     <row r="2893" spans="1:3" x14ac:dyDescent="0.3">
@@ -41161,10 +41161,10 @@
         <v>2892</v>
       </c>
       <c r="B2893" t="s">
-        <v>2924</v>
+        <v>2923</v>
       </c>
       <c r="C2893" t="s">
-        <v>2923</v>
+        <v>2922</v>
       </c>
     </row>
     <row r="2894" spans="1:3" x14ac:dyDescent="0.3">
@@ -41172,10 +41172,10 @@
         <v>2893</v>
       </c>
       <c r="B2894" t="s">
-        <v>2925</v>
+        <v>2924</v>
       </c>
       <c r="C2894" t="s">
-        <v>2923</v>
+        <v>2922</v>
       </c>
     </row>
     <row r="2895" spans="1:3" x14ac:dyDescent="0.3">
@@ -41183,10 +41183,10 @@
         <v>2894</v>
       </c>
       <c r="B2895" t="s">
-        <v>2926</v>
+        <v>2925</v>
       </c>
       <c r="C2895" t="s">
-        <v>2923</v>
+        <v>2922</v>
       </c>
     </row>
     <row r="2896" spans="1:3" x14ac:dyDescent="0.3">
@@ -41194,10 +41194,10 @@
         <v>2895</v>
       </c>
       <c r="B2896" t="s">
-        <v>2927</v>
+        <v>2926</v>
       </c>
       <c r="C2896" t="s">
-        <v>2923</v>
+        <v>2922</v>
       </c>
     </row>
     <row r="2897" spans="1:3" x14ac:dyDescent="0.3">
@@ -41205,10 +41205,10 @@
         <v>2896</v>
       </c>
       <c r="B2897" t="s">
-        <v>2928</v>
+        <v>2927</v>
       </c>
       <c r="C2897" t="s">
-        <v>2923</v>
+        <v>2922</v>
       </c>
     </row>
     <row r="2898" spans="1:3" x14ac:dyDescent="0.3">
@@ -41216,10 +41216,10 @@
         <v>2897</v>
       </c>
       <c r="B2898" t="s">
-        <v>2929</v>
+        <v>2928</v>
       </c>
       <c r="C2898" t="s">
-        <v>2923</v>
+        <v>2922</v>
       </c>
     </row>
     <row r="2899" spans="1:3" x14ac:dyDescent="0.3">
@@ -41227,10 +41227,10 @@
         <v>2898</v>
       </c>
       <c r="B2899" t="s">
-        <v>2930</v>
+        <v>2929</v>
       </c>
       <c r="C2899" t="s">
-        <v>2923</v>
+        <v>2922</v>
       </c>
     </row>
     <row r="2900" spans="1:3" x14ac:dyDescent="0.3">
@@ -41238,10 +41238,10 @@
         <v>2899</v>
       </c>
       <c r="B2900" t="s">
-        <v>2931</v>
+        <v>2930</v>
       </c>
       <c r="C2900" t="s">
-        <v>2923</v>
+        <v>2922</v>
       </c>
     </row>
     <row r="2901" spans="1:3" x14ac:dyDescent="0.3">
@@ -41249,10 +41249,10 @@
         <v>2900</v>
       </c>
       <c r="B2901" t="s">
-        <v>2932</v>
+        <v>2931</v>
       </c>
       <c r="C2901" t="s">
-        <v>2923</v>
+        <v>2922</v>
       </c>
     </row>
     <row r="2902" spans="1:3" x14ac:dyDescent="0.3">
@@ -41260,10 +41260,10 @@
         <v>2901</v>
       </c>
       <c r="B2902" t="s">
-        <v>2933</v>
+        <v>2932</v>
       </c>
       <c r="C2902" t="s">
-        <v>2923</v>
+        <v>2922</v>
       </c>
     </row>
     <row r="2903" spans="1:3" x14ac:dyDescent="0.3">
@@ -41271,10 +41271,10 @@
         <v>2902</v>
       </c>
       <c r="B2903" t="s">
-        <v>2934</v>
+        <v>2933</v>
       </c>
       <c r="C2903" t="s">
-        <v>2923</v>
+        <v>2922</v>
       </c>
     </row>
     <row r="2904" spans="1:3" x14ac:dyDescent="0.3">
@@ -41282,10 +41282,10 @@
         <v>2903</v>
       </c>
       <c r="B2904" t="s">
-        <v>2935</v>
+        <v>2934</v>
       </c>
       <c r="C2904" t="s">
-        <v>2923</v>
+        <v>2922</v>
       </c>
     </row>
     <row r="2905" spans="1:3" x14ac:dyDescent="0.3">
@@ -41293,10 +41293,10 @@
         <v>2904</v>
       </c>
       <c r="B2905" t="s">
-        <v>2936</v>
+        <v>2935</v>
       </c>
       <c r="C2905" t="s">
-        <v>2923</v>
+        <v>2922</v>
       </c>
     </row>
     <row r="2906" spans="1:3" x14ac:dyDescent="0.3">
@@ -41304,10 +41304,10 @@
         <v>2905</v>
       </c>
       <c r="B2906" t="s">
-        <v>2937</v>
+        <v>2936</v>
       </c>
       <c r="C2906" t="s">
-        <v>2923</v>
+        <v>2922</v>
       </c>
     </row>
     <row r="2907" spans="1:3" x14ac:dyDescent="0.3">
@@ -41315,10 +41315,10 @@
         <v>2906</v>
       </c>
       <c r="B2907" t="s">
-        <v>2938</v>
+        <v>2937</v>
       </c>
       <c r="C2907" t="s">
-        <v>2923</v>
+        <v>2922</v>
       </c>
     </row>
     <row r="2908" spans="1:3" x14ac:dyDescent="0.3">
@@ -41326,10 +41326,10 @@
         <v>2907</v>
       </c>
       <c r="B2908" t="s">
-        <v>2939</v>
+        <v>2938</v>
       </c>
       <c r="C2908" t="s">
-        <v>2923</v>
+        <v>2922</v>
       </c>
     </row>
     <row r="2909" spans="1:3" x14ac:dyDescent="0.3">
@@ -41337,10 +41337,10 @@
         <v>2908</v>
       </c>
       <c r="B2909" t="s">
-        <v>2940</v>
+        <v>2939</v>
       </c>
       <c r="C2909" t="s">
-        <v>2923</v>
+        <v>2922</v>
       </c>
     </row>
     <row r="2910" spans="1:3" x14ac:dyDescent="0.3">
@@ -41348,10 +41348,10 @@
         <v>2909</v>
       </c>
       <c r="B2910" t="s">
-        <v>2941</v>
+        <v>2940</v>
       </c>
       <c r="C2910" t="s">
-        <v>2923</v>
+        <v>2922</v>
       </c>
     </row>
     <row r="2911" spans="1:3" x14ac:dyDescent="0.3">
@@ -41359,10 +41359,10 @@
         <v>2910</v>
       </c>
       <c r="B2911" t="s">
-        <v>2942</v>
+        <v>2941</v>
       </c>
       <c r="C2911" t="s">
-        <v>2923</v>
+        <v>2922</v>
       </c>
     </row>
     <row r="2912" spans="1:3" x14ac:dyDescent="0.3">
@@ -41370,10 +41370,10 @@
         <v>2911</v>
       </c>
       <c r="B2912" t="s">
-        <v>2943</v>
+        <v>2942</v>
       </c>
       <c r="C2912" t="s">
-        <v>2923</v>
+        <v>2922</v>
       </c>
     </row>
     <row r="2913" spans="1:3" x14ac:dyDescent="0.3">
@@ -41381,10 +41381,10 @@
         <v>2912</v>
       </c>
       <c r="B2913" t="s">
-        <v>2983</v>
+        <v>2982</v>
       </c>
       <c r="C2913" t="s">
-        <v>2923</v>
+        <v>2922</v>
       </c>
     </row>
     <row r="2914" spans="1:3" x14ac:dyDescent="0.3">
@@ -41392,10 +41392,10 @@
         <v>2913</v>
       </c>
       <c r="B2914" t="s">
-        <v>2984</v>
+        <v>2983</v>
       </c>
       <c r="C2914" t="s">
-        <v>2923</v>
+        <v>2922</v>
       </c>
     </row>
     <row r="2915" spans="1:3" x14ac:dyDescent="0.3">
@@ -41403,10 +41403,10 @@
         <v>2914</v>
       </c>
       <c r="B2915" t="s">
-        <v>2985</v>
+        <v>2984</v>
       </c>
       <c r="C2915" t="s">
-        <v>2923</v>
+        <v>2922</v>
       </c>
     </row>
     <row r="2916" spans="1:3" x14ac:dyDescent="0.3">
@@ -41414,10 +41414,10 @@
         <v>2915</v>
       </c>
       <c r="B2916" t="s">
+        <v>2943</v>
+      </c>
+      <c r="C2916" t="s">
         <v>2944</v>
-      </c>
-      <c r="C2916" t="s">
-        <v>2945</v>
       </c>
     </row>
     <row r="2917" spans="1:3" x14ac:dyDescent="0.3">
@@ -41425,10 +41425,10 @@
         <v>2916</v>
       </c>
       <c r="B2917" t="s">
+        <v>2945</v>
+      </c>
+      <c r="C2917" t="s">
         <v>2946</v>
-      </c>
-      <c r="C2917" t="s">
-        <v>2947</v>
       </c>
     </row>
     <row r="2918" spans="1:3" x14ac:dyDescent="0.3">
@@ -41436,10 +41436,10 @@
         <v>2917</v>
       </c>
       <c r="B2918" t="s">
+        <v>2947</v>
+      </c>
+      <c r="C2918" t="s">
         <v>2948</v>
-      </c>
-      <c r="C2918" t="s">
-        <v>2949</v>
       </c>
     </row>
     <row r="2919" spans="1:3" x14ac:dyDescent="0.3">
@@ -41447,10 +41447,10 @@
         <v>2918</v>
       </c>
       <c r="B2919" t="s">
-        <v>2950</v>
+        <v>2949</v>
       </c>
       <c r="C2919" t="s">
-        <v>2949</v>
+        <v>2948</v>
       </c>
     </row>
     <row r="2920" spans="1:3" x14ac:dyDescent="0.3">
@@ -41458,10 +41458,10 @@
         <v>2919</v>
       </c>
       <c r="B2920" t="s">
+        <v>2950</v>
+      </c>
+      <c r="C2920" t="s">
         <v>2951</v>
-      </c>
-      <c r="C2920" t="s">
-        <v>2952</v>
       </c>
     </row>
     <row r="2921" spans="1:3" x14ac:dyDescent="0.3">
@@ -41469,10 +41469,10 @@
         <v>2920</v>
       </c>
       <c r="B2921" t="s">
-        <v>2953</v>
+        <v>2952</v>
       </c>
       <c r="C2921" t="s">
-        <v>2952</v>
+        <v>2951</v>
       </c>
     </row>
     <row r="2922" spans="1:3" x14ac:dyDescent="0.3">
@@ -41480,10 +41480,10 @@
         <v>2921</v>
       </c>
       <c r="B2922" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="C2922" t="s">
-        <v>2952</v>
+        <v>2951</v>
       </c>
     </row>
     <row r="2923" spans="1:3" x14ac:dyDescent="0.3">
@@ -41491,10 +41491,10 @@
         <v>2922</v>
       </c>
       <c r="B2923" t="s">
-        <v>2955</v>
+        <v>2954</v>
       </c>
       <c r="C2923" t="s">
-        <v>2952</v>
+        <v>2951</v>
       </c>
     </row>
     <row r="2924" spans="1:3" x14ac:dyDescent="0.3">
@@ -41502,10 +41502,10 @@
         <v>2923</v>
       </c>
       <c r="B2924" t="s">
-        <v>2956</v>
+        <v>2955</v>
       </c>
       <c r="C2924" t="s">
-        <v>2952</v>
+        <v>2951</v>
       </c>
     </row>
     <row r="2925" spans="1:3" x14ac:dyDescent="0.3">
@@ -41513,10 +41513,10 @@
         <v>2924</v>
       </c>
       <c r="B2925" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="C2925" t="s">
-        <v>2952</v>
+        <v>2951</v>
       </c>
     </row>
     <row r="2926" spans="1:3" x14ac:dyDescent="0.3">
@@ -41524,10 +41524,10 @@
         <v>2925</v>
       </c>
       <c r="B2926" t="s">
-        <v>2958</v>
+        <v>2957</v>
       </c>
       <c r="C2926" t="s">
-        <v>2952</v>
+        <v>2951</v>
       </c>
     </row>
     <row r="2927" spans="1:3" x14ac:dyDescent="0.3">
@@ -41535,10 +41535,10 @@
         <v>2926</v>
       </c>
       <c r="B2927" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="C2927" t="s">
-        <v>2952</v>
+        <v>2951</v>
       </c>
     </row>
     <row r="2928" spans="1:3" x14ac:dyDescent="0.3">
@@ -41546,10 +41546,10 @@
         <v>2927</v>
       </c>
       <c r="B2928" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="C2928" t="s">
-        <v>2952</v>
+        <v>2951</v>
       </c>
     </row>
     <row r="2929" spans="1:3" x14ac:dyDescent="0.3">
@@ -41557,10 +41557,10 @@
         <v>2928</v>
       </c>
       <c r="B2929" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="C2929" t="s">
-        <v>2952</v>
+        <v>2951</v>
       </c>
     </row>
     <row r="2930" spans="1:3" x14ac:dyDescent="0.3">
@@ -41568,10 +41568,10 @@
         <v>2929</v>
       </c>
       <c r="B2930" t="s">
+        <v>2961</v>
+      </c>
+      <c r="C2930" t="s">
         <v>2962</v>
-      </c>
-      <c r="C2930" t="s">
-        <v>2963</v>
       </c>
     </row>
     <row r="2931" spans="1:3" x14ac:dyDescent="0.3">
@@ -41579,10 +41579,10 @@
         <v>2930</v>
       </c>
       <c r="B2931" t="s">
-        <v>2964</v>
+        <v>2963</v>
       </c>
       <c r="C2931" t="s">
-        <v>2963</v>
+        <v>2962</v>
       </c>
     </row>
     <row r="2932" spans="1:3" x14ac:dyDescent="0.3">
@@ -41590,10 +41590,10 @@
         <v>2931</v>
       </c>
       <c r="B2932" t="s">
-        <v>2965</v>
+        <v>2964</v>
       </c>
       <c r="C2932" t="s">
-        <v>2963</v>
+        <v>2962</v>
       </c>
     </row>
     <row r="2933" spans="1:3" x14ac:dyDescent="0.3">
@@ -41601,10 +41601,10 @@
         <v>2932</v>
       </c>
       <c r="B2933" t="s">
-        <v>2966</v>
+        <v>2965</v>
       </c>
       <c r="C2933" t="s">
-        <v>2963</v>
+        <v>2962</v>
       </c>
     </row>
     <row r="2934" spans="1:3" x14ac:dyDescent="0.3">
@@ -41612,10 +41612,10 @@
         <v>2933</v>
       </c>
       <c r="B2934" t="s">
-        <v>2967</v>
+        <v>2966</v>
       </c>
       <c r="C2934" t="s">
-        <v>2963</v>
+        <v>2962</v>
       </c>
     </row>
     <row r="2935" spans="1:3" x14ac:dyDescent="0.3">
@@ -41623,10 +41623,10 @@
         <v>2934</v>
       </c>
       <c r="B2935" t="s">
-        <v>2968</v>
+        <v>2967</v>
       </c>
       <c r="C2935" t="s">
-        <v>2963</v>
+        <v>2962</v>
       </c>
     </row>
     <row r="2936" spans="1:3" x14ac:dyDescent="0.3">
@@ -41634,10 +41634,10 @@
         <v>2935</v>
       </c>
       <c r="B2936" t="s">
-        <v>2969</v>
+        <v>2968</v>
       </c>
       <c r="C2936" t="s">
-        <v>2963</v>
+        <v>2962</v>
       </c>
     </row>
     <row r="2937" spans="1:3" x14ac:dyDescent="0.3">
@@ -41645,10 +41645,10 @@
         <v>2936</v>
       </c>
       <c r="B2937" t="s">
-        <v>2970</v>
+        <v>2969</v>
       </c>
       <c r="C2937" t="s">
-        <v>2963</v>
+        <v>2962</v>
       </c>
     </row>
     <row r="2938" spans="1:3" x14ac:dyDescent="0.3">
@@ -41656,10 +41656,10 @@
         <v>2937</v>
       </c>
       <c r="B2938" t="s">
-        <v>2971</v>
+        <v>2970</v>
       </c>
       <c r="C2938" t="s">
-        <v>2963</v>
+        <v>2962</v>
       </c>
     </row>
     <row r="2939" spans="1:3" x14ac:dyDescent="0.3">
@@ -41667,10 +41667,10 @@
         <v>2938</v>
       </c>
       <c r="B2939" t="s">
-        <v>2972</v>
+        <v>2971</v>
       </c>
       <c r="C2939" t="s">
-        <v>2963</v>
+        <v>2962</v>
       </c>
     </row>
     <row r="2940" spans="1:3" x14ac:dyDescent="0.3">
@@ -41678,10 +41678,10 @@
         <v>2939</v>
       </c>
       <c r="B2940" t="s">
-        <v>2973</v>
+        <v>2972</v>
       </c>
       <c r="C2940" t="s">
-        <v>2963</v>
+        <v>2962</v>
       </c>
     </row>
     <row r="2941" spans="1:3" x14ac:dyDescent="0.3">
@@ -41689,10 +41689,10 @@
         <v>2940</v>
       </c>
       <c r="B2941" t="s">
-        <v>2974</v>
+        <v>2973</v>
       </c>
       <c r="C2941" t="s">
-        <v>2963</v>
+        <v>2962</v>
       </c>
     </row>
     <row r="2942" spans="1:3" x14ac:dyDescent="0.3">
@@ -41700,10 +41700,10 @@
         <v>2941</v>
       </c>
       <c r="B2942" t="s">
-        <v>2975</v>
+        <v>2974</v>
       </c>
       <c r="C2942" t="s">
-        <v>2963</v>
+        <v>2962</v>
       </c>
     </row>
     <row r="2943" spans="1:3" x14ac:dyDescent="0.3">
@@ -41711,10 +41711,10 @@
         <v>2942</v>
       </c>
       <c r="B2943" t="s">
-        <v>2976</v>
+        <v>2975</v>
       </c>
       <c r="C2943" t="s">
-        <v>2963</v>
+        <v>2962</v>
       </c>
     </row>
     <row r="2944" spans="1:3" x14ac:dyDescent="0.3">
@@ -41722,10 +41722,10 @@
         <v>2943</v>
       </c>
       <c r="B2944" t="s">
-        <v>2977</v>
+        <v>2976</v>
       </c>
       <c r="C2944" t="s">
-        <v>2963</v>
+        <v>2962</v>
       </c>
     </row>
     <row r="2945" spans="1:3" x14ac:dyDescent="0.3">
@@ -41733,10 +41733,10 @@
         <v>2944</v>
       </c>
       <c r="B2945" t="s">
-        <v>2978</v>
+        <v>2977</v>
       </c>
       <c r="C2945" t="s">
-        <v>2963</v>
+        <v>2962</v>
       </c>
     </row>
     <row r="2946" spans="1:3" x14ac:dyDescent="0.3">
@@ -41744,10 +41744,10 @@
         <v>2945</v>
       </c>
       <c r="B2946" t="s">
-        <v>2979</v>
+        <v>2978</v>
       </c>
       <c r="C2946" t="s">
-        <v>2963</v>
+        <v>2962</v>
       </c>
     </row>
     <row r="2947" spans="1:3" x14ac:dyDescent="0.3">
@@ -41755,10 +41755,10 @@
         <v>2946</v>
       </c>
       <c r="B2947" t="s">
-        <v>2980</v>
+        <v>2979</v>
       </c>
       <c r="C2947" t="s">
-        <v>2963</v>
+        <v>2962</v>
       </c>
     </row>
     <row r="2948" spans="1:3" x14ac:dyDescent="0.3">
@@ -41766,10 +41766,10 @@
         <v>2947</v>
       </c>
       <c r="B2948" t="s">
-        <v>2981</v>
+        <v>2980</v>
       </c>
       <c r="C2948" t="s">
-        <v>2963</v>
+        <v>2962</v>
       </c>
     </row>
     <row r="2949" spans="1:3" x14ac:dyDescent="0.3">
@@ -41777,10 +41777,10 @@
         <v>2948</v>
       </c>
       <c r="B2949" t="s">
-        <v>2982</v>
+        <v>2981</v>
       </c>
       <c r="C2949" t="s">
-        <v>2963</v>
+        <v>2962</v>
       </c>
     </row>
     <row r="2950" spans="1:3" x14ac:dyDescent="0.3">
@@ -41788,10 +41788,10 @@
         <v>2949</v>
       </c>
       <c r="B2950" t="s">
-        <v>2986</v>
+        <v>2985</v>
       </c>
       <c r="C2950" t="s">
-        <v>2605</v>
+        <v>2604</v>
       </c>
     </row>
     <row r="2951" spans="1:3" x14ac:dyDescent="0.3">
@@ -41799,10 +41799,10 @@
         <v>2950</v>
       </c>
       <c r="B2951" t="s">
-        <v>2987</v>
+        <v>2986</v>
       </c>
       <c r="C2951" t="s">
-        <v>2923</v>
+        <v>2922</v>
       </c>
     </row>
     <row r="2952" spans="1:3" x14ac:dyDescent="0.3">
@@ -41810,7 +41810,7 @@
         <v>2951</v>
       </c>
       <c r="B2952" t="s">
-        <v>2988</v>
+        <v>2987</v>
       </c>
       <c r="C2952" t="s">
         <v>2188</v>
@@ -41821,7 +41821,7 @@
         <v>2952</v>
       </c>
       <c r="B2953" t="s">
-        <v>2989</v>
+        <v>2988</v>
       </c>
       <c r="C2953" t="s">
         <v>4</v>
@@ -41832,7 +41832,7 @@
         <v>2953</v>
       </c>
       <c r="B2954" t="s">
-        <v>2990</v>
+        <v>2989</v>
       </c>
       <c r="C2954" t="s">
         <v>293</v>
@@ -41843,7 +41843,7 @@
         <v>2954</v>
       </c>
       <c r="B2955" t="s">
-        <v>2991</v>
+        <v>2990</v>
       </c>
       <c r="C2955" t="s">
         <v>2188</v>
@@ -41854,7 +41854,7 @@
         <v>2955</v>
       </c>
       <c r="B2956" t="s">
-        <v>2992</v>
+        <v>2991</v>
       </c>
       <c r="C2956" t="s">
         <v>2188</v>
@@ -41865,7 +41865,7 @@
         <v>2956</v>
       </c>
       <c r="B2957" t="s">
-        <v>2993</v>
+        <v>2992</v>
       </c>
       <c r="C2957" t="s">
         <v>2188</v>
@@ -41876,7 +41876,7 @@
         <v>2957</v>
       </c>
       <c r="B2958" t="s">
-        <v>2994</v>
+        <v>2993</v>
       </c>
       <c r="C2958" t="s">
         <v>2374</v>
@@ -41887,10 +41887,10 @@
         <v>2958</v>
       </c>
       <c r="B2959" t="s">
-        <v>2995</v>
+        <v>2994</v>
       </c>
       <c r="C2959" t="s">
-        <v>2945</v>
+        <v>2944</v>
       </c>
     </row>
   </sheetData>

--- a/pujk.xlsx
+++ b/pujk.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OJK\Penugasan 2\acara\gencar\monev\olah data\coding\running\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC3A356A-2A00-49D8-9DE8-7D9604440174}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6D80178-26B6-4844-837B-58CA58611611}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5919" uniqueCount="2996">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5923" uniqueCount="2998">
   <si>
     <t>No</t>
   </si>
@@ -9021,6 +9021,12 @@
   </si>
   <si>
     <t>PT BPRS FITRAH</t>
+  </si>
+  <si>
+    <t>PT Pranata Karya Solusi</t>
+  </si>
+  <si>
+    <t>PT Arganis Konsultindo</t>
   </si>
 </sst>
 </file>
@@ -9338,7 +9344,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C2959"/>
+  <dimension ref="A1:C2961"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="8.88671875" customWidth="1"/>
@@ -41893,6 +41899,28 @@
         <v>2944</v>
       </c>
     </row>
+    <row r="2960" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2960">
+        <v>2959</v>
+      </c>
+      <c r="B2960" t="s">
+        <v>2996</v>
+      </c>
+      <c r="C2960" t="s">
+        <v>2946</v>
+      </c>
+    </row>
+    <row r="2961" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2961">
+        <v>2960</v>
+      </c>
+      <c r="B2961" t="s">
+        <v>2997</v>
+      </c>
+      <c r="C2961" t="s">
+        <v>2948</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
